--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,32 +692,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -726,19 +726,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -746,32 +746,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -780,19 +780,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -800,23 +800,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -834,19 +834,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -854,7 +854,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N8" t="n">
         <v>6</v>
@@ -900,7 +900,7 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -908,17 +908,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -942,19 +942,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -962,53 +962,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24</v>
+      </c>
+      <c r="M10" t="n">
         <v>25</v>
       </c>
-      <c r="D10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>32</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1016,26 +1016,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-2</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1062,36 +1062,34 @@
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1106,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1118,7 +1116,7 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1126,23 +1124,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1160,7 +1158,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1172,7 +1170,7 @@
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1180,20 +1178,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1205,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1234,26 +1232,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1265,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1288,26 +1286,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1322,10 +1320,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1334,7 +1332,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1342,32 +1340,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1376,19 +1374,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1396,24 +1394,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
@@ -1430,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1442,7 +1440,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1450,7 +1448,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1460,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1469,13 +1467,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1484,27 +1482,29 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1514,7 +1514,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1523,54 +1523,52 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1579,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1591,22 +1589,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1614,21 +1612,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
@@ -1639,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1648,19 +1646,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1668,56 +1666,1300 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Tom Curran</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>17</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nathan Sowter</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>16</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
         <v>-2</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>4</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1732,7 +2974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1803,55 +3045,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -1860,112 +3102,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1974,17 +3216,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D13" t="n">
         <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1993,17 +3235,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
         <v>2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -2012,17 +3254,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -2031,17 +3273,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2050,17 +3292,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2069,52 +3311,52 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -2126,14 +3368,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2145,14 +3387,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2164,19 +3406,171 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Richard Gleeson</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2191,7 +3585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2251,7 +3645,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2267,14 +3661,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -2283,14 +3677,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -2299,7 +3693,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2331,14 +3725,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2347,14 +3741,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -2363,14 +3757,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2379,14 +3773,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2395,14 +3789,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2411,14 +3805,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -2427,7 +3821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2443,7 +3837,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2459,7 +3853,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2475,7 +3869,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2491,7 +3885,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -2507,7 +3901,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -2523,7 +3917,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -2539,7 +3933,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -2555,7 +3949,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -2565,6 +3959,134 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nathan Sowter</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2938,14 +4460,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Match starts at Jul 22, 17:30 GMT</t>
+          <t>Welsh Fire won by 6 wkts</t>
         </is>
       </c>
       <c r="C25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -3063,10 +4585,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>London Spirit vs Manchester Originals, 3rd Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>London Spirit vs Manchester Super Giants, 3rd Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Match starts at Jul 23, 17:30 GMT</t>
+        </is>
+      </c>
       <c r="C34" t="b">
         <v>0</v>
       </c>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Top_Runs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Top_Wickets" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Matches" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Match_Player_Points" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4101,517 +4102,1171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>MatchNo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Match</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Processed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MI London vs Sunrisers Leeds, 1st Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>MI London won by 7 wkts</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Southern Brave vs Welsh Fire, 2nd Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Welsh Fire won by 6 wkts</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MatchNo</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Match</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Started</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Processed</t>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>MatchPoints</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MI London vs Sunrisers Leeds, 1st Match, The Hundred Mens Competition 2026</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MI London won by 7 wkts</t>
-        </is>
-      </c>
-      <c r="C2" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" t="b">
-        <v>1</v>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Mitchell Marsh</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>67</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Birmingham Phoenix vs Sunrisers Leeds, 24th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Sam Curran</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Welsh Fire vs London Spirit, 31st Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ryan Rickelton</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tbc vs Tbc, Eliminator, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>London Spirit vs Birmingham Phoenix, 28th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Nathan Sowter</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Birmingham Phoenix vs Mi London, 32nd Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="b">
-        <v>0</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trent Rockets vs Birmingham Phoenix, 22nd Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D8" t="b">
-        <v>0</v>
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Manchester Super Giants vs Welsh Fire, 21st Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" t="b">
-        <v>0</v>
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Trent Rockets vs Sunrisers Leeds, 17th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" t="b">
-        <v>0</v>
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Tom Alsop</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>London Spirit vs Mi London, 23rd Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" t="b">
-        <v>0</v>
+      <c r="A11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Manchester Super Giants vs Sunrisers Leeds, 30th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" t="b">
-        <v>0</v>
+      <c r="A12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sunrisers Leeds vs Welsh Fire, 27th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="b">
-        <v>0</v>
+      <c r="A13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nicholas Pooran</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Southern Brave vs Mi London, 9th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" t="b">
-        <v>0</v>
+      <c r="A14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Brydon Carse</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sunrisers Leeds vs London Spirit, 20th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" t="b">
-        <v>0</v>
+      <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Mi London vs Manchester Super Giants, 18th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" t="b">
-        <v>0</v>
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Birmingham Phoenix vs Trent Rockets, 4th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="b">
-        <v>0</v>
-      </c>
-      <c r="D17" t="b">
-        <v>0</v>
+      <c r="A17" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nathan Ellis</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sunrisers Leeds vs Manchester Super Giants, 10th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" t="b">
-        <v>0</v>
+      <c r="A18" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Birmingham Phoenix vs Welsh Fire, 15th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" t="b">
-        <v>0</v>
+      <c r="A19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tom Curran</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Welsh Fire vs Trent Rockets, 12th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" t="b">
-        <v>0</v>
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Richard Gleeson</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>122</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>London Spirit vs Southern Brave, 16th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" t="b">
-        <v>0</v>
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Trent Rockets vs Southern Brave, 29th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="b">
-        <v>0</v>
-      </c>
-      <c r="D22" t="b">
-        <v>0</v>
+      <c r="A22" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Manchester Super Giants vs Trent Rockets, 14th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" t="b">
-        <v>0</v>
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Manchester Super Giants vs Birmingham Phoenix, 7th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" t="b">
-        <v>0</v>
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Southern Brave vs Welsh Fire, 2nd Match, The Hundred Mens Competition 2026</t>
-        </is>
+      <c r="A25" t="n">
+        <v>2</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Welsh Fire won by 6 wkts</t>
-        </is>
-      </c>
-      <c r="C25" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sam Cook</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Mi London vs Trent Rockets, 25th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="b">
-        <v>0</v>
-      </c>
-      <c r="D26" t="b">
-        <v>0</v>
+      <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Southern Brave vs Manchester Super Giants, 26th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Rachin Ravindra</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Southern Brave vs Birmingham Phoenix, 13th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Thomas Rew</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Tbc vs Tbc, Final, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" t="b">
-        <v>0</v>
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Matthew Short</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Welsh Fire vs Southern Brave, 19th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
+      <c r="A30" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>66</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sunrisers Leeds vs Southern Brave, 5th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="b">
-        <v>0</v>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
+      <c r="A31" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Welsh Fire vs Mi London, 6th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
+      <c r="A32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Welsh Fire vs Trent Rockets, 11th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>London Spirit vs Manchester Super Giants, 3rd Match, The Hundred Mens Competition 2026</t>
-        </is>
+      <c r="A34" t="n">
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Match starts at Jul 23, 17:30 GMT</t>
-        </is>
-      </c>
-      <c r="C34" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Nikhil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>87</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Trent Rockets vs London Spirit, 8th Match, The Hundred Mens Competition 2026</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="b">
-        <v>0</v>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
+      <c r="A35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Chris Woakes</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Philip Salt</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Daniel Worrall</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,96 +417,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Balls</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fours</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sixes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Maidens</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RunOuts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Batting_Points</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Bowling_Points</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fielding_Points</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Lineup_Points</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Base_Points</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Fifties</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Ducks</t>
         </is>
@@ -527,23 +515,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -558,22 +546,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="M2" t="n">
         <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -583,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -617,150 +605,152 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
+        <v>88</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>22</v>
       </c>
-      <c r="M5" t="n">
-        <v>61</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -772,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -781,52 +771,54 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -835,19 +827,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -855,20 +847,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -880,28 +872,28 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>53</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -909,17 +901,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -943,10 +935,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -955,7 +947,7 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -963,26 +955,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -997,10 +989,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -1009,7 +1001,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1017,20 +1009,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -1042,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1051,19 +1043,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1071,26 +1063,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1105,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1117,7 +1109,7 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1125,26 +1117,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1156,22 +1148,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1179,53 +1171,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1233,20 +1225,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1258,28 +1250,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1287,26 +1279,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1321,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1333,7 +1325,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1341,32 +1333,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1375,19 +1367,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1395,26 +1387,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1429,10 +1421,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1441,7 +1433,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1449,26 +1441,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1483,10 +1475,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-2</v>
+        <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1495,42 +1487,40 @@
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1539,19 +1529,19 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1559,7 +1549,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1596,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N21" t="n">
         <v>6</v>
@@ -1605,7 +1595,7 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1613,32 +1603,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1647,19 +1637,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1667,7 +1657,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1692,7 +1682,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1707,13 +1697,13 @@
         <v>25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1721,26 +1711,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1755,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1767,7 +1757,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -1775,23 +1765,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1800,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1809,19 +1799,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1829,26 +1819,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1860,22 +1850,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1883,26 +1873,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1917,10 +1907,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -1929,61 +1919,63 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>25</v>
+      </c>
+      <c r="N28" t="n">
         <v>6</v>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>10</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" t="n">
         <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -1991,26 +1983,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2022,22 +2014,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2045,17 +2037,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -2064,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -2076,22 +2068,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2099,26 +2091,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2133,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2145,7 +2137,7 @@
         <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2153,17 +2145,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -2172,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2187,19 +2179,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2207,20 +2199,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2241,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2253,7 +2245,7 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2261,20 +2253,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2286,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2295,19 +2287,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2315,23 +2307,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2346,22 +2338,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2369,23 +2361,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2403,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2415,7 +2407,7 @@
         <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2423,21 +2415,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
@@ -2448,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2457,45 +2449,43 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>-2</v>
+        <v>19</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2513,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -2525,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2533,17 +2523,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -2558,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2567,19 +2557,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O39" t="n">
         <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2587,53 +2577,53 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>7</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>4</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
         <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2641,23 +2631,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2675,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2687,7 +2677,7 @@
         <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2695,20 +2685,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2729,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2741,7 +2731,7 @@
         <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2749,20 +2739,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2783,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2795,7 +2785,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2803,23 +2793,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2837,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2849,7 +2839,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2857,20 +2847,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2891,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2903,7 +2893,7 @@
         <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2911,56 +2901,1358 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>8</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>8</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>8</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P51" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Peter Willey</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>8</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4</v>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4</v>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Willey</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>6</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>8</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>4</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4</v>
+      </c>
+      <c r="P59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4</v>
+      </c>
+      <c r="P60" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4</v>
+      </c>
+      <c r="P61" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4</v>
+      </c>
+      <c r="P64" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4</v>
+      </c>
+      <c r="P66" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4</v>
+      </c>
+      <c r="P68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
         <v>-2</v>
       </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>4</v>
-      </c>
-      <c r="P46" t="n">
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2979,27 +4271,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Fours</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Sixes</t>
         </is>
@@ -3008,112 +4300,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
         <v>5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -3122,36 +4414,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -3160,55 +4452,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -3217,14 +4509,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -3236,17 +4528,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3255,17 +4547,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3274,36 +4566,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -3312,17 +4604,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -3331,17 +4623,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -3350,17 +4642,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -3369,17 +4661,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -3388,36 +4680,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -3426,17 +4718,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -3445,17 +4737,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -3464,52 +4756,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -3521,17 +4813,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -3540,17 +4832,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -3559,14 +4851,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -3590,22 +4882,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Maidens</t>
         </is>
@@ -3630,7 +4922,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -3646,7 +4938,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3662,7 +4954,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3678,7 +4970,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -3694,14 +4986,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -3710,14 +5002,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -3726,14 +5018,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -3742,14 +5034,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -3758,7 +5050,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3774,7 +5066,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3790,7 +5082,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3806,7 +5098,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3822,14 +5114,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -3838,14 +5130,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -3854,14 +5146,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3870,14 +5162,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -3886,14 +5178,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -3902,14 +5194,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -3918,14 +5210,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -3934,14 +5226,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -3950,14 +5242,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -3966,7 +5258,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3982,7 +5274,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3998,7 +5290,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4014,7 +5306,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4030,7 +5322,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4046,7 +5338,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4062,7 +5354,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4078,7 +5370,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -4102,36 +5394,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MatchNo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Processed</t>
         </is>
@@ -4190,6 +5482,34 @@
         </is>
       </c>
       <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>London Spirit vs Manchester Super Giants, 3rd Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Manchester Super Giants won by 7 runs</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4204,31 +5524,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MatchNo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MatchPoints</t>
         </is>
@@ -5267,6 +6587,558 @@
       </c>
       <c r="E46" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Adam Milne</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>3</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Peter Willey</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Jos Buttler</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>3</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Adam Zampa</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>3</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Heinrich Klaasen</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Liam Livingstone</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>3</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Leus du Plooy</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>James Coles</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>3</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>3</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Liam Dawson</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Gus Atkinson</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Josh Tongue</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Willey</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>David Willey</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lhuan-dre Pretorius</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Kiran Carlson</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sonny Baker</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Dewald Brevis</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,23 +681,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -712,22 +712,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -737,23 +737,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -762,28 +762,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -793,32 +793,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -827,52 +827,54 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -881,40 +883,42 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -935,10 +939,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -947,7 +951,7 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -955,26 +959,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -989,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -1001,7 +1005,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -1009,32 +1013,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1043,19 +1047,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1063,26 +1067,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1097,10 +1101,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1109,15 +1113,17 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1142,13 +1148,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1157,13 +1163,13 @@
         <v>53</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1171,17 +1177,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1205,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1217,7 +1223,7 @@
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1225,26 +1231,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1259,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>8</v>
@@ -1271,7 +1277,7 @@
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1279,23 +1285,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1313,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1325,7 +1331,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1333,23 +1339,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1367,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1379,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1387,32 +1393,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1421,19 +1427,19 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1441,23 +1447,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1466,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1475,19 +1481,19 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1495,53 +1501,53 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1549,7 +1555,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1568,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1586,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N21" t="n">
         <v>6</v>
@@ -1595,7 +1601,7 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1603,17 +1609,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1622,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1637,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1649,7 +1655,7 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1657,20 +1663,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1691,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M23" t="n">
         <v>25</v>
@@ -1703,7 +1709,7 @@
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1711,26 +1717,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1745,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -1757,7 +1763,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -1765,23 +1771,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1799,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1811,7 +1817,7 @@
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1819,17 +1825,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -1838,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1850,22 +1856,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1873,20 +1879,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1907,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
         <v>33</v>
@@ -1919,36 +1925,34 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1960,22 +1964,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -1983,23 +1987,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -2008,28 +2012,28 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
         <v>25</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2037,53 +2041,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="M30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O30" t="n">
         <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2091,7 +2095,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2122,22 +2126,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
         <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2145,26 +2149,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -2176,22 +2180,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2199,26 +2203,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2233,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>8</v>
@@ -2245,7 +2249,7 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2253,26 +2257,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2287,10 +2291,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2299,7 +2303,7 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2307,26 +2311,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2341,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2353,7 +2357,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2361,26 +2365,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2392,22 +2396,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2415,23 +2419,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2449,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2461,7 +2465,7 @@
         <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2469,26 +2473,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2500,22 +2504,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2523,7 +2527,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2542,34 +2546,34 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2577,32 +2581,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2611,46 +2615,48 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2662,22 +2668,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2685,26 +2691,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2719,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2731,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2739,26 +2745,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2773,10 +2779,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -2785,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2793,26 +2799,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2827,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -2839,7 +2845,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2847,26 +2853,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2881,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -2893,7 +2899,7 @@
         <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2901,20 +2907,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2935,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -2947,7 +2953,7 @@
         <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -2955,17 +2961,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2974,13 +2980,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2989,19 +2995,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3009,20 +3015,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -3040,22 +3046,22 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3063,20 +3069,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -3097,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3109,7 +3115,7 @@
         <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3117,23 +3123,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -3142,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3151,19 +3157,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3171,23 +3177,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3196,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -3205,19 +3211,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3225,20 +3231,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -3250,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3259,19 +3265,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3279,14 +3285,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
         <v>2</v>
@@ -3295,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3313,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -3325,17 +3331,15 @@
         <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3360,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -3375,13 +3379,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O54" t="n">
         <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -3389,20 +3393,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3414,28 +3418,28 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3443,23 +3447,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -3468,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3477,42 +3481,40 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3533,7 +3535,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -3545,7 +3547,7 @@
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3553,20 +3555,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3584,45 +3586,43 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3663,7 +3663,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -3673,7 +3673,7 @@
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -3688,7 +3688,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3703,13 +3703,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
         <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3717,20 +3717,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3763,7 +3763,7 @@
         <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3771,23 +3771,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -3817,7 +3817,7 @@
         <v>4</v>
       </c>
       <c r="P62" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3825,17 +3825,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3859,19 +3859,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
         <v>4</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3879,17 +3879,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3913,19 +3913,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
         <v>4</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3933,23 +3933,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>4</v>
       </c>
       <c r="P65" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -3987,17 +3987,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -4018,22 +4018,22 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
         <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4041,7 +4041,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4081,13 +4081,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4095,7 +4095,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4135,13 +4135,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O68" t="n">
         <v>4</v>
       </c>
       <c r="P68" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4149,7 +4149,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -4174,7 +4174,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4189,13 +4189,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4203,56 +4203,1196 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4</v>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>8</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4</v>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>6</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4</v>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Willey</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>6</v>
+      </c>
+      <c r="O74" t="n">
+        <v>4</v>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4</v>
+      </c>
+      <c r="P76" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4</v>
+      </c>
+      <c r="P77" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>6</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4</v>
+      </c>
+      <c r="P78" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="n">
+        <v>9</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4</v>
+      </c>
+      <c r="P79" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4</v>
+      </c>
+      <c r="P80" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="P81" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>4</v>
+      </c>
+      <c r="P82" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4</v>
+      </c>
+      <c r="P83" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>4</v>
+      </c>
+      <c r="P84" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4</v>
+      </c>
+      <c r="P85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>4</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>4</v>
+      </c>
+      <c r="P87" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4</v>
+      </c>
+      <c r="P88" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>4</v>
+      </c>
+      <c r="P89" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>4</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>-2</v>
       </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>4</v>
-      </c>
-      <c r="P70" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>4</v>
+      </c>
+      <c r="P91" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4319,36 +5459,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -4357,17 +5497,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -4376,280 +5516,280 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D20" t="n">
         <v>2</v>
@@ -4661,17 +5801,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -4680,14 +5820,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -4699,17 +5839,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -4718,36 +5858,36 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -4756,17 +5896,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -4775,36 +5915,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -4813,36 +5953,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -4851,20 +5991,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4970,7 +6110,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -4986,7 +6126,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5002,7 +6142,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5018,7 +6158,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -5034,7 +6174,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -5050,14 +6190,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -5066,14 +6206,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -5082,14 +6222,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -5098,7 +6238,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -5114,7 +6254,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -5130,7 +6270,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -5146,7 +6286,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -5178,7 +6318,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -5210,7 +6350,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5226,7 +6366,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -5242,7 +6382,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -5258,14 +6398,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -5274,14 +6414,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -5290,14 +6430,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -5306,14 +6446,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -5322,14 +6462,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5338,14 +6478,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -5354,14 +6494,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -5370,7 +6510,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -5394,7 +6534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5510,6 +6650,34 @@
         </is>
       </c>
       <c r="F4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Birmingham Phoenix vs Trent Rockets, 4th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Birmingham Phoenix won by 10 runs</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5524,7 +6692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7141,6 +8309,489 @@
         <v>28</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Joe Clarke</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Tom Banton</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Will Smeed</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Craig Overton</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Rehan Ahmed</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Finn Allen</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Donovan Ferreira</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Mitchell Owen</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Calvin Harrison</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sean Dickson</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Mohammad Amir</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lewis Gregory</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Scott Currie</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Sam Billings</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ben Dwarshuis</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Usman Tariq</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,32 +515,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -549,19 +549,19 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -571,24 +571,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
@@ -602,22 +602,22 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -627,32 +627,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -661,52 +661,54 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -715,98 +717,98 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -818,28 +820,28 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>34</v>
+      </c>
+      <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
       <c r="P7" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -849,26 +851,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -883,48 +885,46 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -939,52 +939,54 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="M9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -993,52 +995,54 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>98</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>16</v>
       </c>
-      <c r="M10" t="n">
-        <v>53</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8</v>
-      </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1047,46 +1051,48 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1101,54 +1107,52 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1157,52 +1161,54 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M13" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1211,52 +1217,54 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1265,19 +1273,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>8</v>
       </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
       <c r="P15" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1285,23 +1293,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1310,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1319,19 +1327,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1339,23 +1347,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1373,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1382,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1393,53 +1401,53 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N18" t="n">
+        <v>18</v>
+      </c>
+      <c r="O18" t="n">
         <v>8</v>
       </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
       <c r="P18" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1447,23 +1455,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1481,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1490,10 +1498,10 @@
         <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1501,23 +1509,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1526,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1535,19 +1543,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M20" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1555,20 +1563,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1580,28 +1588,28 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
         <v>53</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1609,26 +1617,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1643,10 +1651,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="M22" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1655,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1663,32 +1671,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1697,43 +1705,45 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="M23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>47</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1742,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1751,19 +1761,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -1771,32 +1781,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1805,19 +1815,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1825,7 +1835,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1850,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1865,13 +1875,13 @@
         <v>53</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1879,26 +1889,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1913,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -1925,7 +1935,7 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -1933,26 +1943,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1964,22 +1974,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -1987,26 +1997,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
+        <v>43</v>
+      </c>
+      <c r="D29" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" t="n">
         <v>6</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2021,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>8</v>
@@ -2033,7 +2043,7 @@
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2041,23 +2051,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2066,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2095,26 +2105,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -2126,22 +2136,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2149,53 +2159,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>9</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>28</v>
-      </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2203,32 +2213,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2237,19 +2247,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>8</v>
       </c>
-      <c r="O33" t="n">
-        <v>4</v>
-      </c>
       <c r="P33" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2257,26 +2267,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2291,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M34" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2303,7 +2313,7 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2311,26 +2321,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2345,10 +2355,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M35" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2357,7 +2367,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2365,17 +2375,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -2384,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2396,22 +2406,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2419,32 +2429,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2453,19 +2463,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2473,7 +2483,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2492,7 +2502,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2504,22 +2514,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2527,17 +2537,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -2546,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2558,22 +2568,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2581,32 +2591,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2615,39 +2625,37 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>-2</v>
+        <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -2656,7 +2664,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2668,49 +2676,51 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2722,22 +2732,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="M42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2745,26 +2755,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2779,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="M43" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -2791,7 +2801,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2799,7 +2809,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2818,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2836,7 +2846,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -2845,7 +2855,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2853,20 +2863,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2878,7 +2888,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2887,19 +2897,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
         <v>25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2907,26 +2917,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2938,22 +2948,22 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N46" t="n">
+        <v>14</v>
+      </c>
+      <c r="O46" t="n">
         <v>8</v>
       </c>
-      <c r="O46" t="n">
-        <v>4</v>
-      </c>
       <c r="P46" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -2961,20 +2971,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2995,10 +3005,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3007,7 +3017,7 @@
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3015,32 +3025,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3049,19 +3059,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O48" t="n">
         <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3069,32 +3079,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3103,19 +3113,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
         <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3123,26 +3133,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -3157,19 +3167,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3177,17 +3187,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -3202,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -3211,19 +3221,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3231,14 +3241,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D52" t="n">
         <v>18</v>
@@ -3247,7 +3257,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3256,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3265,19 +3275,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O52" t="n">
         <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3285,53 +3295,53 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6</v>
+      </c>
+      <c r="O53" t="n">
         <v>8</v>
       </c>
-      <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>10</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>8</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4</v>
-      </c>
       <c r="P53" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3339,20 +3349,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3373,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3382,64 +3392,66 @@
         <v>16</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
+        <v>22</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>28</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
         <v>6</v>
       </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>7</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>8</v>
-      </c>
       <c r="O55" t="n">
         <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3447,26 +3459,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -3481,10 +3493,10 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -3493,7 +3505,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3501,26 +3513,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3532,22 +3544,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3555,26 +3567,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -3586,22 +3598,22 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3609,26 +3621,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3643,10 +3655,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -3655,7 +3667,7 @@
         <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3663,17 +3675,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -3682,13 +3694,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3697,19 +3709,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3717,26 +3729,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3751,10 +3763,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3763,7 +3775,7 @@
         <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3775,49 +3787,49 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
+        <v>11</v>
+      </c>
+      <c r="D62" t="n">
+        <v>13</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>13</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
         <v>8</v>
       </c>
-      <c r="D62" t="n">
-        <v>7</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>10</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3825,17 +3837,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3844,13 +3856,13 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3859,19 +3871,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>4</v>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3879,20 +3891,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3904,7 +3916,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3913,19 +3925,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>4</v>
       </c>
       <c r="P64" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3933,23 +3945,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3958,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3967,19 +3979,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -3987,23 +3999,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4018,22 +4030,22 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4041,20 +4053,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -4066,7 +4078,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4075,19 +4087,19 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="O67" t="n">
-        <v>4</v>
-      </c>
       <c r="P67" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4099,7 +4111,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -4120,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4135,13 +4147,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
+        <v>16</v>
+      </c>
+      <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="O68" t="n">
-        <v>4</v>
-      </c>
       <c r="P68" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4149,23 +4161,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4174,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4183,19 +4195,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4203,23 +4215,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -4237,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -4249,7 +4261,7 @@
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4257,23 +4269,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -4282,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4291,19 +4303,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>4</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4311,7 +4323,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -4321,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -4336,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4345,42 +4357,40 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
         <v>4</v>
       </c>
       <c r="P72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4398,43 +4408,45 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -4446,28 +4458,28 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O74" t="n">
         <v>4</v>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -4475,23 +4487,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -4500,7 +4512,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -4509,42 +4521,40 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>4</v>
       </c>
       <c r="P75" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -4565,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -4577,7 +4587,7 @@
         <v>4</v>
       </c>
       <c r="P76" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -4585,7 +4595,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4595,7 +4605,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -4610,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4625,13 +4635,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
         <v>4</v>
       </c>
       <c r="P77" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -4639,17 +4649,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -4664,48 +4674,46 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -4720,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4729,19 +4737,19 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
         <v>4</v>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -4749,17 +4757,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -4774,7 +4782,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4783,19 +4791,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4803,17 +4811,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -4837,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -4846,10 +4854,10 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -4857,17 +4865,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -4891,7 +4899,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -4903,7 +4911,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4911,17 +4919,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -4942,22 +4950,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O83" t="n">
         <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -4965,17 +4973,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -5008,10 +5016,10 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -5019,53 +5027,53 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>6</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4</v>
+      </c>
+      <c r="P85" t="n">
         <v>10</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>1</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>4</v>
-      </c>
-      <c r="P85" t="n">
-        <v>5</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5073,7 +5081,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -5083,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -5098,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5107,27 +5115,29 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
         <v>4</v>
       </c>
       <c r="P86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -5137,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -5158,40 +5168,42 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O87" t="n">
         <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -5215,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5227,7 +5239,7 @@
         <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5235,17 +5247,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -5269,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -5281,7 +5293,7 @@
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5289,17 +5301,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5323,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5335,7 +5347,7 @@
         <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5343,56 +5355,218 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>4</v>
+      </c>
+      <c r="P91" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
         <v>-2</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
-        <v>4</v>
-      </c>
-      <c r="P91" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="n">
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4</v>
+      </c>
+      <c r="P94" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5440,74 +5614,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -5516,169 +5690,169 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
         <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -5687,36 +5861,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -5725,90 +5899,90 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -5820,93 +5994,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -5915,17 +6089,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -5934,77 +6108,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6050,10 +6224,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -6062,14 +6236,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6078,14 +6252,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6094,11 +6268,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -6110,11 +6284,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -6126,7 +6300,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6142,7 +6316,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6162,7 +6336,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -6190,11 +6364,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
@@ -6206,7 +6380,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6222,7 +6396,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6238,14 +6412,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -6254,14 +6428,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -6274,10 +6448,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -6286,14 +6460,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6302,14 +6476,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6318,14 +6492,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6334,14 +6508,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6350,14 +6524,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6366,11 +6540,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -6382,11 +6556,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -6398,7 +6572,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6414,7 +6588,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6430,11 +6604,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -6446,11 +6620,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -6462,7 +6636,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6478,11 +6652,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -6494,11 +6668,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -6510,14 +6684,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -6534,7 +6708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6678,6 +6852,62 @@
         </is>
       </c>
       <c r="F5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sunrisers Leeds vs Southern Brave, 5th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sunrisers Leeds won by 5 runs</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Welsh Fire vs MI London, 6th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Welsh Fire won by 15 runs</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6692,7 +6922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8792,6 +9022,995 @@
         <v>57</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>5</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Mitchell Marsh</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>5</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>5</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Ryan Rickelton</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>5</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Daniel Worrall</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>5</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>5</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>5</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>5</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Tom Alsop</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>5</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>5</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>5</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>5</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>5</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>5</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>5</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Matthew Revis</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>5</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Nikhil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>5</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Brydon Carse</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>5</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>5</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>5</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Nathan Ellis</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>6</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Philip Salt</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>6</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Sherfane Rutherford</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>6</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Matthew Short</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>6</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Richard Gleeson</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>6</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>6</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Nicholas Pooran</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>6</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Rachin Ravindra</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>6</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>6</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>6</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>6</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>6</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Tom Curran</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>6</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Sam Curran</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>6</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>6</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>6</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>6</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>6</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>6</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>6</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Chris Woakes</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>6</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Sam Cook</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,32 +515,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -549,19 +549,19 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -571,32 +571,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -605,19 +605,19 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -627,23 +627,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -673,7 +673,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -683,26 +683,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -717,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>8</v>
@@ -729,44 +729,42 @@
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -775,43 +773,47 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>161</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -820,28 +822,28 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -851,7 +853,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -870,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -888,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -897,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -905,20 +907,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -930,7 +932,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -939,19 +941,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -961,23 +963,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -989,25 +991,25 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -1017,32 +1019,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1051,49 +1053,47 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1127,26 +1127,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1161,45 +1161,43 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1217,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1229,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1239,7 +1237,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1258,13 +1256,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1276,16 +1274,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1293,87 +1291,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
+        <v>48</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>63</v>
+      </c>
+      <c r="M16" t="n">
         <v>53</v>
       </c>
-      <c r="D16" t="n">
-        <v>42</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>64</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -1381,19 +1381,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1401,26 +1401,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1432,46 +1432,48 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1489,7 +1491,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1501,31 +1503,33 @@
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -1534,7 +1538,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1543,19 +1547,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1563,23 +1567,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -1597,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M21" t="n">
         <v>53</v>
@@ -1606,10 +1610,10 @@
         <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1617,32 +1621,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1651,19 +1655,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1671,27 +1675,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -1705,42 +1709,40 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -1761,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1773,34 +1775,36 @@
         <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1815,10 +1819,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>8</v>
@@ -1827,7 +1831,7 @@
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1839,16 +1843,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1869,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M26" t="n">
         <v>53</v>
@@ -1878,10 +1882,10 @@
         <v>16</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1889,26 +1893,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1923,46 +1927,48 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1974,22 +1980,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -1997,23 +2003,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
+        <v>62</v>
+      </c>
+      <c r="D29" t="n">
         <v>43</v>
       </c>
-      <c r="D29" t="n">
-        <v>17</v>
-      </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2022,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2031,19 +2037,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2051,23 +2057,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2076,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2085,19 +2091,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
         <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2105,23 +2111,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2130,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2139,19 +2145,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2159,23 +2165,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -2190,22 +2196,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O32" t="n">
         <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2213,53 +2219,53 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="M33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O33" t="n">
         <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2267,23 +2273,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2292,55 +2298,57 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2355,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2367,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2375,32 +2383,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2409,19 +2417,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M36" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
         <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2429,7 +2437,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2439,7 +2447,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -2454,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2466,16 +2474,16 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2483,32 +2491,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2517,19 +2525,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M38" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2537,7 +2545,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2547,43 +2555,43 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
         <v>5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>4</v>
       </c>
       <c r="M39" t="n">
         <v>53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2591,23 +2599,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2616,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2625,19 +2633,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2645,20 +2653,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2679,10 +2687,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>-2</v>
+        <v>13</v>
       </c>
       <c r="M41" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2691,33 +2699,31 @@
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2732,22 +2738,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2755,26 +2761,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2789,19 +2795,19 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2809,53 +2815,53 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M44" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2863,7 +2869,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2873,22 +2879,22 @@
         <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2897,19 +2903,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M45" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2917,7 +2923,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -2927,7 +2933,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2936,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2951,10 +2957,10 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N46" t="n">
         <v>14</v>
@@ -2963,25 +2969,27 @@
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -2990,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -3005,19 +3013,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M47" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3025,32 +3033,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3059,52 +3067,54 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3113,19 +3123,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3133,53 +3143,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
         <v>9</v>
       </c>
-      <c r="D50" t="n">
-        <v>6</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>10</v>
-      </c>
       <c r="M50" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3187,26 +3197,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -3221,10 +3231,10 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N51" t="n">
         <v>8</v>
@@ -3233,7 +3243,7 @@
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3241,32 +3251,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3275,19 +3285,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P52" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3295,17 +3305,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -3314,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3326,22 +3336,22 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3349,32 +3359,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3383,19 +3393,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N54" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
@@ -3405,53 +3415,53 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3459,32 +3469,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3493,19 +3503,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M56" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3513,17 +3523,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -3532,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3544,22 +3554,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3567,32 +3577,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3601,19 +3611,19 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M58" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3621,26 +3631,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3652,22 +3662,22 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="M59" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3675,17 +3685,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -3700,28 +3710,28 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60" t="n">
         <v>25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3729,11 +3739,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -3748,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3766,16 +3776,16 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3783,20 +3793,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D62" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -3808,7 +3818,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3817,19 +3827,19 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P62" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3837,20 +3847,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3862,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3871,19 +3881,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M63" t="n">
         <v>25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3891,32 +3901,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3925,19 +3935,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3945,23 +3955,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3970,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3979,19 +3989,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -3999,20 +4009,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -4033,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -4042,10 +4052,10 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4053,61 +4063,63 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
+        <v>26</v>
+      </c>
+      <c r="D67" t="n">
+        <v>17</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>29</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
         <v>14</v>
       </c>
-      <c r="D67" t="n">
-        <v>10</v>
-      </c>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>16</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" t="n">
         <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -4126,34 +4138,34 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4161,23 +4173,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4186,7 +4198,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4195,19 +4207,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4215,53 +4227,53 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>25</v>
+      </c>
+      <c r="N70" t="n">
         <v>16</v>
-      </c>
-      <c r="D70" t="n">
-        <v>11</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>19</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4269,32 +4281,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4306,16 +4318,16 @@
         <v>10</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4323,23 +4335,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -4348,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4357,19 +4369,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -4377,32 +4389,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4411,45 +4423,43 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4467,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4479,7 +4489,7 @@
         <v>4</v>
       </c>
       <c r="P74" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -4487,26 +4497,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -4518,22 +4528,22 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -4541,17 +4551,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -4566,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4581,31 +4591,33 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O76" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -4614,13 +4626,13 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4629,43 +4641,45 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -4683,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -4692,10 +4706,10 @@
         <v>8</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -4703,23 +4717,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -4737,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -4746,10 +4760,10 @@
         <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -4757,20 +4771,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -4791,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -4800,10 +4814,10 @@
         <v>8</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P80" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4811,53 +4825,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
+        <v>19</v>
+      </c>
+      <c r="D81" t="n">
+        <v>19</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>22</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
         <v>4</v>
       </c>
-      <c r="D81" t="n">
-        <v>4</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>4</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>8</v>
-      </c>
       <c r="P81" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -4865,17 +4879,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -4890,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4899,19 +4913,19 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4919,20 +4933,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4950,22 +4964,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -4973,20 +4987,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -5007,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -5019,15 +5033,17 @@
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -5052,13 +5068,13 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -5067,13 +5083,13 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
         <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5081,17 +5097,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -5106,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5115,42 +5131,40 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5168,42 +5182,40 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="n">
-        <v>1</v>
-      </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -5227,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5236,10 +5248,10 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5247,17 +5259,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -5272,7 +5284,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5281,19 +5293,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5301,17 +5313,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5335,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5344,10 +5356,10 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5355,7 +5367,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5380,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -5395,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5409,7 +5421,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -5440,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5449,13 +5461,13 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O92" t="n">
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5463,7 +5475,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5494,7 +5506,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5503,13 +5515,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O93" t="n">
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5517,7 +5529,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5527,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -5542,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5557,16 +5569,180 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O94" t="n">
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>8</v>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>4</v>
+      </c>
+      <c r="P96" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>4</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5614,77 +5790,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
         <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
         <v>9</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -5694,108 +5870,108 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
         <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
         <v>5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -5804,150 +5980,150 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
         <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
         <v>4</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
         <v>3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>5</v>
@@ -5956,55 +6132,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
@@ -6013,33 +6189,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
@@ -6051,17 +6227,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -6070,17 +6246,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -6089,36 +6265,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
         <v>5</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -6127,58 +6303,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6236,7 +6412,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -6252,14 +6428,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6268,14 +6444,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6284,14 +6460,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6300,14 +6476,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6316,14 +6492,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6332,14 +6508,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6348,14 +6524,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6364,7 +6540,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6380,11 +6556,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -6396,11 +6572,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
@@ -6412,7 +6588,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6428,7 +6604,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6444,7 +6620,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6460,11 +6636,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
@@ -6476,11 +6652,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>2</v>
@@ -6492,11 +6668,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
@@ -6508,7 +6684,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6524,7 +6700,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6540,14 +6716,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -6556,14 +6732,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -6572,14 +6748,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -6588,14 +6764,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -6604,14 +6780,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -6620,14 +6796,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -6636,14 +6812,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -6652,14 +6828,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -6668,14 +6844,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -6688,10 +6864,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -6708,7 +6884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6908,6 +7084,62 @@
         </is>
       </c>
       <c r="F7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Manchester Super Giants vs Birmingham Phoenix, 7th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Manchester Super Giants won by 87 runs</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trent Rockets vs London Spirit, 8th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trent Rockets won by 4 wkts</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -6922,7 +7154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10011,6 +10243,1018 @@
         <v>29</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>7</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>7</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Rehan Ahmed</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>7</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>7</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Joe Clarke</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>7</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Jos Buttler</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>7</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Ben Dwarshuis</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>7</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Heinrich Klaasen</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>7</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Donovan Ferreira</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>7</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Leus du Plooy</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>7</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Mitchell Owen</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>7</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>7</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Liam Dawson</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>7</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>7</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Scott Currie</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>7</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Usman Tariq</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>7</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Will Smeed</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>7</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Josh Tongue</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>7</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Laurie Evans</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>7</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Gus Atkinson</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>7</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Sean Dickson</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>7</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>7</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Sonny Baker</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>8</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Lhuan-dre Pretorius</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>8</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Sam Billings</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>8</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Jonny Bairstow</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>8</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Craig Overton</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>8</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>8</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>8</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Liam Livingstone</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>8</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>8</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Dewald Brevis</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>8</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>8</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>James Coles</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>8</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>8</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Calvin Harrison</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>8</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>David Willey</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>8</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Finn Allen</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>8</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Andrew Tye</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>8</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Lewis Gregory</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>8</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Adam Milne</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>8</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Mohammad Amir</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>8</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Tom Banton</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>8</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>8</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Adam Zampa</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,26 +515,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -546,57 +546,59 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -605,19 +607,19 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -627,32 +629,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -661,75 +663,73 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -739,26 +739,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -773,10 +773,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="M6" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>8</v>
@@ -785,38 +785,36 @@
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -825,60 +823,58 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>161</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -887,43 +883,45 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -932,28 +930,28 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -967,13 +965,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -994,78 +992,80 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>94</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>12</v>
       </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>16</v>
-      </c>
-      <c r="M11" t="n">
-        <v>106</v>
-      </c>
-      <c r="N11" t="n">
-        <v>16</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
       <c r="P11" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1073,32 +1073,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1107,43 +1107,45 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
@@ -1152,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1161,19 +1163,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M13" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1181,63 +1183,61 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1274,16 +1274,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1291,32 +1291,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1325,75 +1325,73 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="M16" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="M17" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1401,27 +1399,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>4</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -1432,51 +1430,49 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>123</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1491,10 +1487,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="N19" t="n">
         <v>8</v>
@@ -1503,42 +1499,40 @@
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1547,46 +1541,48 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="M20" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1601,19 +1597,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1621,26 +1617,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1655,52 +1651,56 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="M22" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1709,52 +1709,54 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1763,55 +1765,53 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -1819,19 +1819,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1839,26 +1839,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1873,40 +1873,42 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="M26" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>16</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -1918,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1927,19 +1929,19 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -1949,32 +1951,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1983,19 +1985,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2003,32 +2005,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2037,19 +2039,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2057,32 +2059,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2091,19 +2093,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2111,23 +2113,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2136,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2145,19 +2147,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2165,74 +2167,76 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M32" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -2250,22 +2254,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2273,82 +2277,80 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -2363,43 +2365,45 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="M35" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D36" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2408,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2417,19 +2421,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -2437,32 +2441,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2471,19 +2475,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M37" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2491,26 +2495,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2522,22 +2526,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="M38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2545,20 +2549,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -2570,28 +2574,28 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2599,23 +2603,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E40" t="n">
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2624,61 +2628,63 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2687,19 +2693,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2707,53 +2713,53 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2761,17 +2767,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2795,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -2807,7 +2813,7 @@
         <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2815,23 +2821,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -2846,22 +2852,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="M44" t="n">
         <v>25</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O44" t="n">
         <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2869,26 +2875,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2903,40 +2909,42 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="M45" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P45" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2948,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2957,42 +2965,40 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -3013,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -3025,7 +3031,7 @@
         <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3033,23 +3039,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -3058,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3067,42 +3073,40 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3123,10 +3127,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M49" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3135,7 +3139,7 @@
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3143,53 +3147,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="M50" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3197,23 +3201,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -3222,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -3231,19 +3235,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M51" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3251,7 +3255,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3261,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -3276,61 +3280,63 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M52" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O52" t="n">
         <v>8</v>
       </c>
       <c r="P52" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D53" t="n">
+        <v>19</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
         <v>5</v>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3339,37 +3345,39 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="M53" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -3393,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
         <v>58</v>
@@ -3405,42 +3413,40 @@
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3449,19 +3455,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M55" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N55" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3469,32 +3475,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3503,19 +3509,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3523,17 +3529,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -3557,7 +3563,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" t="n">
         <v>53</v>
@@ -3569,7 +3575,7 @@
         <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3577,53 +3583,53 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3631,26 +3637,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3662,76 +3668,78 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>45</v>
+        <v>-2</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="M60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3739,17 +3747,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -3773,10 +3781,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3785,7 +3793,7 @@
         <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3793,53 +3801,53 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
+        <v>34</v>
+      </c>
+      <c r="D62" t="n">
+        <v>19</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
         <v>41</v>
       </c>
-      <c r="D62" t="n">
-        <v>30</v>
-      </c>
-      <c r="E62" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>53</v>
-      </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3847,32 +3855,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3881,19 +3889,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3901,14 +3909,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>6</v>
@@ -3917,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -3926,28 +3934,28 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M64" t="n">
         <v>25</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O64" t="n">
         <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3955,23 +3963,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D65" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -3989,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -3998,10 +4006,10 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P65" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -4009,23 +4017,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D66" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4043,7 +4051,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -4055,7 +4063,7 @@
         <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4063,26 +4071,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -4094,51 +4102,49 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O67" t="n">
         <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4153,10 +4159,10 @@
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M68" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>14</v>
@@ -4165,31 +4171,33 @@
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D69" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4198,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4207,19 +4215,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4227,11 +4235,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -4252,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4267,13 +4275,13 @@
         <v>25</v>
       </c>
       <c r="N70" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4281,32 +4289,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4315,19 +4323,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M71" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4335,32 +4343,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4369,19 +4377,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P72" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -4389,20 +4397,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4414,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4423,19 +4431,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M73" t="n">
         <v>25</v>
       </c>
       <c r="N73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4443,20 +4451,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D74" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -4477,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -4486,10 +4494,10 @@
         <v>8</v>
       </c>
       <c r="O74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -4497,7 +4505,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4522,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4537,13 +4545,13 @@
         <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
         <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -4551,20 +4559,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -4576,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4585,29 +4593,27 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O76" t="n">
         <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -4617,7 +4623,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -4638,48 +4644,46 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>25</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -4688,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4697,52 +4701,54 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
         <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4751,27 +4757,29 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -4781,13 +4789,13 @@
         <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -4805,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -4817,7 +4825,7 @@
         <v>8</v>
       </c>
       <c r="P80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4825,23 +4833,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -4850,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4859,19 +4867,19 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -4879,23 +4887,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4904,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4913,19 +4921,19 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O82" t="n">
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4933,23 +4941,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4967,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -4976,10 +4984,10 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -4987,20 +4995,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -5012,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -5021,39 +5029,37 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O84" t="n">
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -5068,28 +5074,28 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5097,20 +5103,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -5131,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -5143,10 +5149,12 @@
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5205,53 +5213,53 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
+        <v>13</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>11</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>8</v>
+      </c>
+      <c r="P88" t="n">
         <v>19</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>7</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
-        <v>8</v>
-      </c>
-      <c r="P88" t="n">
-        <v>15</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5259,17 +5267,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -5293,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -5305,7 +5313,7 @@
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5313,17 +5321,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5347,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -5359,7 +5367,7 @@
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5367,7 +5375,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -5421,17 +5429,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -5452,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -5461,21 +5469,23 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -5500,13 +5510,13 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -5515,13 +5525,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5585,17 +5595,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -5616,19 +5626,19 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
         <v>10</v>
@@ -5639,17 +5649,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -5673,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -5685,7 +5695,7 @@
         <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5693,7 +5703,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -5703,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -5724,25 +5734,133 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="n">
+      <c r="R97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>4</v>
+      </c>
+      <c r="P98" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>4</v>
+      </c>
+      <c r="P99" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5885,55 +6003,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -5942,93 +6060,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
+        <v>7</v>
+      </c>
+      <c r="E12" t="n">
         <v>5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -6037,283 +6155,283 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
         <v>4</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D28" t="n">
         <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -6322,39 +6440,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6400,10 +6518,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -6412,11 +6530,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
@@ -6428,11 +6546,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -6444,7 +6562,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6460,11 +6578,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -6476,14 +6594,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6492,14 +6610,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6508,14 +6626,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6524,14 +6642,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6540,14 +6658,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -6556,14 +6674,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -6572,14 +6690,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -6588,14 +6706,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -6604,14 +6722,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -6620,7 +6738,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6636,7 +6754,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6652,7 +6770,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6668,11 +6786,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>2</v>
@@ -6684,7 +6802,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6700,7 +6818,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6716,11 +6834,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
         <v>2</v>
@@ -6732,7 +6850,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6748,7 +6866,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6780,7 +6898,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -6796,7 +6914,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -6812,7 +6930,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6828,7 +6946,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -6844,7 +6962,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -6884,7 +7002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7140,6 +7258,34 @@
         </is>
       </c>
       <c r="F9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Southern Brave vs MI London, 9th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MI London won by 3 wkts</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7154,7 +7300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11255,6 +11401,512 @@
         <v>4</v>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>9</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>9</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>9</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>9</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Ollie Pope</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>9</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>9</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Sherfane Rutherford</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>9</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>9</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Nathan Sowter</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>9</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>9</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>9</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Nikhil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>9</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>9</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Saif Zaib</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>9</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>9</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>9</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>9</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Nicholas Pooran</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>9</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Tom Curran</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>9</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>9</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Richard Gleeson</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>9</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Sam Curran</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>9</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,26 +515,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -549,10 +549,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="M2" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>8</v>
@@ -561,38 +561,36 @@
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -604,51 +602,53 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -657,58 +657,60 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M4" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -717,19 +719,19 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -739,32 +741,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -773,99 +775,99 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>160</v>
+      </c>
+      <c r="M7" t="n">
         <v>25</v>
       </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>48</v>
-      </c>
-      <c r="M7" t="n">
-        <v>124</v>
-      </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>215</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -883,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -895,7 +897,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -905,26 +907,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -933,133 +935,127 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>161</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>155</v>
+      </c>
+      <c r="N10" t="n">
         <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>106</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>40</v>
       </c>
       <c r="O10" t="n">
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O11" t="n">
         <v>12</v>
@@ -1067,38 +1063,42 @@
       <c r="P11" t="n">
         <v>158</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1107,54 +1107,52 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1163,97 +1161,101 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="M13" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O13" t="n">
         <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="M14" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
@@ -1262,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1271,19 +1273,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1295,7 +1297,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -1334,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1345,53 +1347,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1399,20 +1401,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1430,22 +1432,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>111</v>
+      </c>
+      <c r="N18" t="n">
         <v>18</v>
-      </c>
-      <c r="M18" t="n">
-        <v>103</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6</v>
       </c>
       <c r="O18" t="n">
         <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1453,26 +1455,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1484,22 +1486,22 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M19" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1507,79 +1509,77 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" t="n">
+        <v>103</v>
+      </c>
+      <c r="N20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>122</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8</v>
-      </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1597,40 +1597,42 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>137</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D22" t="n">
         <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -1642,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1651,56 +1653,52 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1709,54 +1707,54 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="M23" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1765,52 +1763,56 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="M24" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1819,52 +1821,54 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="M25" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="N25" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1873,54 +1877,52 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1929,54 +1931,52 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1985,19 +1985,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2005,14 +2005,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2039,52 +2039,54 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="M29" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2093,43 +2095,45 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="M30" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2138,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2147,19 +2151,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2167,20 +2171,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -2192,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2201,54 +2205,56 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2257,19 +2263,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O33" t="n">
         <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2277,32 +2283,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2311,19 +2317,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="N34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2331,23 +2337,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D35" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2356,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2365,45 +2371,43 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D36" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2412,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2421,52 +2425,54 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2475,19 +2481,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2495,53 +2501,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N38" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2549,32 +2555,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>61</v>
+      </c>
+      <c r="D39" t="n">
+        <v>47</v>
+      </c>
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="C39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2583,19 +2589,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="M39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2603,23 +2609,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -2634,42 +2640,40 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E41" t="n">
         <v>4</v>
@@ -2684,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2693,73 +2697,75 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="M42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2767,53 +2773,53 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M43" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O43" t="n">
         <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2821,32 +2827,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2855,19 +2861,19 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2875,23 +2881,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D45" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2900,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2909,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
         <v>12</v>
       </c>
       <c r="P45" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
@@ -2931,32 +2937,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2965,52 +2971,54 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="M46" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D47" t="n">
+        <v>30</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
         <v>3</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3019,19 +3027,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="M47" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O47" t="n">
         <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3039,53 +3047,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3093,20 +3101,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3127,10 +3135,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3139,7 +3147,7 @@
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3147,53 +3155,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N50" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3201,32 +3209,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -3235,19 +3243,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="M51" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3255,23 +3263,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -3280,54 +3288,52 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="M52" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N52" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -3336,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3345,19 +3351,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
@@ -3367,53 +3373,53 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
         <v>5</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2</v>
-      </c>
       <c r="M54" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -3421,23 +3427,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
+        <v>11</v>
+      </c>
+      <c r="D55" t="n">
         <v>7</v>
       </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -3455,19 +3461,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M55" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3475,53 +3481,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M56" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O56" t="n">
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3529,26 +3535,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -3563,10 +3569,10 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="M57" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -3575,7 +3581,7 @@
         <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3583,71 +3589,73 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>50</v>
+      </c>
+      <c r="N58" t="n">
         <v>14</v>
-      </c>
-      <c r="D58" t="n">
-        <v>12</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>15</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25</v>
-      </c>
-      <c r="N58" t="n">
-        <v>16</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -3671,7 +3679,7 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>58</v>
@@ -3683,63 +3691,61 @@
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9</v>
+      </c>
+      <c r="M60" t="n">
+        <v>53</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>4</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>48</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>8</v>
-      </c>
-      <c r="O60" t="n">
-        <v>8</v>
-      </c>
       <c r="P60" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3747,17 +3753,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -3781,10 +3787,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -3793,7 +3799,7 @@
         <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3801,23 +3807,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3832,22 +3838,22 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
         <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3855,32 +3861,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3889,19 +3895,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M63" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" t="n">
         <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3909,32 +3915,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2</v>
       </c>
       <c r="C64" t="n">
+        <v>34</v>
+      </c>
+      <c r="D64" t="n">
+        <v>19</v>
+      </c>
+      <c r="E64" t="n">
         <v>3</v>
       </c>
-      <c r="D64" t="n">
-        <v>6</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3943,19 +3949,19 @@
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="M64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O64" t="n">
         <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3963,26 +3969,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3997,19 +4003,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
         <v>53</v>
       </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -4017,23 +4023,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D66" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4051,7 +4057,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -4060,10 +4066,10 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4071,14 +4077,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
         <v>6</v>
@@ -4087,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -4096,28 +4102,28 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
         <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O67" t="n">
         <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4125,109 +4131,107 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D69" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>53</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>4</v>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>43</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>8</v>
-      </c>
       <c r="P69" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4235,7 +4239,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -4260,13 +4264,13 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4275,13 +4279,13 @@
         <v>25</v>
       </c>
       <c r="N70" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4289,53 +4293,53 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10</v>
+      </c>
+      <c r="M71" t="n">
+        <v>25</v>
+      </c>
+      <c r="N71" t="n">
+        <v>8</v>
+      </c>
+      <c r="O71" t="n">
         <v>12</v>
       </c>
-      <c r="E71" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>22</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>16</v>
-      </c>
-      <c r="O71" t="n">
-        <v>8</v>
-      </c>
       <c r="P71" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4343,23 +4347,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -4368,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4377,19 +4381,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M72" t="n">
         <v>25</v>
       </c>
       <c r="N72" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -4397,26 +4401,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -4431,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="M73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -4443,7 +4447,7 @@
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4451,23 +4455,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -4482,30 +4486,32 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -4536,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4545,13 +4551,13 @@
         <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -4559,20 +4565,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -4584,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4593,19 +4599,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="O76" t="n">
         <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -4613,53 +4619,53 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -4667,32 +4673,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4701,29 +4707,27 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N78" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O78" t="n">
         <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4733,7 +4737,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -4742,13 +4746,13 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4757,75 +4761,73 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N80" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O80" t="n">
         <v>8</v>
       </c>
       <c r="P80" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4833,20 +4835,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D81" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4858,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4867,52 +4869,54 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O81" t="n">
         <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4921,43 +4925,45 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -4966,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -4975,19 +4981,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -4995,23 +5001,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -5020,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -5029,19 +5035,19 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O84" t="n">
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -5049,23 +5055,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5080,22 +5086,22 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5103,20 +5109,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -5128,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5137,42 +5143,40 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -5190,22 +5194,22 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O87" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -5267,20 +5271,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -5292,7 +5296,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5301,19 +5305,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5321,17 +5325,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5346,7 +5350,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -5355,19 +5359,19 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5429,17 +5433,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -5454,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5469,33 +5473,31 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O92" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P92" t="n">
         <v>12</v>
       </c>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="n">
-        <v>1</v>
-      </c>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -5510,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5525,21 +5527,23 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P93" t="n">
         <v>12</v>
       </c>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5549,7 +5553,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -5573,7 +5577,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -5585,17 +5589,15 @@
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -5605,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -5620,22 +5622,22 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
         <v>4</v>
@@ -5644,52 +5646,54 @@
         <v>10</v>
       </c>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
         <v>6</v>
-      </c>
-      <c r="D96" t="n">
-        <v>7</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>6</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>4</v>
@@ -5703,17 +5707,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -5734,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -5757,7 +5761,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -5788,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5797,13 +5801,13 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -5811,7 +5815,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tymal Mills</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -5821,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -5845,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -5857,10 +5861,64 @@
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="n">
+      <c r="R99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>4</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5908,77 +5966,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -6003,55 +6061,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>4</v>
@@ -6060,36 +6118,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>4</v>
@@ -6098,77 +6156,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
         <v>5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6178,105 +6236,105 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
         <v>5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D20" t="n">
         <v>3</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D21" t="n">
         <v>4</v>
@@ -6288,131 +6346,131 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -6421,17 +6479,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -6440,39 +6498,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6530,14 +6588,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6546,7 +6604,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6562,11 +6620,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
@@ -6578,7 +6636,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6594,7 +6652,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6610,11 +6668,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -6674,14 +6732,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -6690,14 +6748,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -6706,7 +6764,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -6722,11 +6780,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -6738,14 +6796,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -6754,14 +6812,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6770,7 +6828,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6786,7 +6844,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -6802,7 +6860,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6818,7 +6876,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6834,11 +6892,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>2</v>
@@ -6850,7 +6908,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -6866,7 +6924,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -6882,11 +6940,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -6930,7 +6988,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -6946,11 +7004,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
@@ -6962,11 +7020,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -6978,7 +7036,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7002,7 +7060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7286,6 +7344,34 @@
         </is>
       </c>
       <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sunrisers Leeds vs Manchester Super Giants, 10th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sunrisers Leeds won by 8 wkts</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7300,7 +7386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E200"/>
+  <dimension ref="A1:E221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11907,6 +11993,489 @@
         <v>37</v>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>10</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>10</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>10</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>10</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Ed Barnard</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>10</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Jos Buttler</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>10</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Heinrich Klaasen</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>10</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Matthew Revis</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>10</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>10</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Brydon Carse</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>10</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>10</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Nathan Ellis</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>10</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>10</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Mitchell Marsh</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>10</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Sonny Baker</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>10</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Ryan Rickelton</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>10</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>10</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>10</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Gus Atkinson</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>10</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Josh Tongue</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>10</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Liam Dawson</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>10</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,81 +571,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -654,28 +652,28 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -685,26 +683,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -716,51 +714,53 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -769,58 +769,60 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M6" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E7" t="n">
         <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -829,19 +831,19 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -851,32 +853,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -885,102 +887,102 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>133</v>
+      </c>
+      <c r="D9" t="n">
+        <v>95</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>184</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>36</v>
-      </c>
-      <c r="D9" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48</v>
-      </c>
-      <c r="M9" t="n">
-        <v>124</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -995,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M10" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -1007,98 +1009,96 @@
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>124</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>106</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>40</v>
-      </c>
-      <c r="O11" t="n">
-        <v>12</v>
-      </c>
       <c r="P11" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1107,19 +1107,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1127,144 +1127,144 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>78</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>88</v>
-      </c>
-      <c r="D13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
+        <v>109</v>
+      </c>
+      <c r="D15" t="n">
+        <v>78</v>
+      </c>
+      <c r="E15" t="n">
         <v>12</v>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1273,46 +1273,50 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>144</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
         <v>16</v>
       </c>
-      <c r="M15" t="n">
-        <v>106</v>
-      </c>
-      <c r="N15" t="n">
-        <v>16</v>
-      </c>
-      <c r="O15" t="n">
-        <v>8</v>
-      </c>
       <c r="P15" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1327,10 +1331,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1339,7 +1343,7 @@
         <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1347,23 +1351,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
@@ -1372,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1381,19 +1385,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M17" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1401,26 +1405,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1432,76 +1436,78 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="M18" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1509,87 +1515,89 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="M20" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
-        <v>89</v>
-      </c>
-      <c r="D21" t="n">
-        <v>46</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -1597,45 +1605,43 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1644,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1653,43 +1659,45 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>137</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1698,7 +1706,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1707,45 +1715,43 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1754,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1763,56 +1769,52 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1821,42 +1823,40 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M26" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1897,53 +1897,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="M27" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="O27" t="n">
         <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -1951,23 +1951,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>4</v>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1985,19 +1985,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M28" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2005,32 +2005,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2039,45 +2039,43 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-2</v>
+        <v>109</v>
       </c>
       <c r="M29" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O29" t="n">
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
         <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2092,58 +2090,58 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>5</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
@@ -2151,19 +2149,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2171,23 +2169,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2205,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2217,44 +2215,42 @@
         <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2263,19 +2259,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2283,26 +2279,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2317,10 +2313,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="N34" t="n">
         <v>8</v>
@@ -2329,41 +2325,43 @@
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>4</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
@@ -2371,19 +2369,19 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N35" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2391,32 +2389,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2425,54 +2423,52 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2481,19 +2477,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="M37" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2501,32 +2497,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2535,43 +2531,45 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="M38" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -2580,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2589,19 +2587,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2609,26 +2607,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2643,10 +2641,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N40" t="n">
         <v>8</v>
@@ -2655,7 +2653,7 @@
         <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2663,32 +2661,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2697,45 +2695,43 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P41" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2744,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2753,73 +2749,77 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="n">
+        <v>61</v>
+      </c>
+      <c r="D43" t="n">
+        <v>53</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>2</v>
       </c>
-      <c r="C43" t="n">
-        <v>45</v>
-      </c>
-      <c r="D43" t="n">
-        <v>34</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2827,32 +2827,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
+        <v>53</v>
+      </c>
+      <c r="D44" t="n">
+        <v>29</v>
+      </c>
+      <c r="E44" t="n">
         <v>4</v>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2861,185 +2861,183 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="M44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>53</v>
-      </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>12</v>
       </c>
       <c r="P45" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
         <v>2</v>
       </c>
-      <c r="C47" t="n">
-        <v>45</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>50</v>
+      </c>
+      <c r="N47" t="n">
         <v>30</v>
       </c>
-      <c r="E47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>55</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>16</v>
-      </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P47" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3047,53 +3045,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="N48" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3101,20 +3099,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -3126,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3135,19 +3133,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M49" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O49" t="n">
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3155,32 +3153,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3189,19 +3187,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="M50" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
         <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3209,32 +3207,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -3243,52 +3241,54 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="M51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3297,19 +3297,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="M52" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O52" t="n">
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3317,26 +3317,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3351,10 +3351,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3363,30 +3363,28 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3398,28 +3396,28 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -3427,32 +3425,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3461,19 +3459,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3481,53 +3479,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>2</v>
       </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
       <c r="L56" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="M56" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O56" t="n">
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3539,16 +3537,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -3569,7 +3567,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -3578,10 +3576,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P57" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3589,17 +3587,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -3614,64 +3612,62 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>39</v>
+      </c>
+      <c r="D59" t="n">
+        <v>20</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>2</v>
       </c>
-      <c r="C59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
@@ -3679,73 +3675,75 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="M59" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O59" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" t="n">
         <v>7</v>
       </c>
-      <c r="D60" t="n">
-        <v>5</v>
-      </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>2</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M60" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P60" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3753,20 +3751,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3784,22 +3782,22 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3807,20 +3805,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D62" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3838,76 +3836,78 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
         <v>2</v>
       </c>
-      <c r="C63" t="n">
-        <v>14</v>
-      </c>
       <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>61</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>12</v>
       </c>
-      <c r="E63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>15</v>
-      </c>
-      <c r="M63" t="n">
-        <v>25</v>
-      </c>
-      <c r="N63" t="n">
-        <v>16</v>
-      </c>
-      <c r="O63" t="n">
-        <v>8</v>
-      </c>
       <c r="P63" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
         <v>34</v>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3955,13 +3955,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P64" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3969,20 +3969,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
         <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -4003,19 +4003,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M65" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -4023,20 +4023,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D66" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -4057,19 +4057,19 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4077,53 +4077,53 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
         <v>2</v>
       </c>
-      <c r="C67" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N67" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P67" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4131,26 +4131,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="n">
+        <v>48</v>
+      </c>
+      <c r="D68" t="n">
+        <v>34</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
         <v>2</v>
       </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -4165,73 +4165,75 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4239,32 +4241,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -4273,52 +4275,54 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4327,19 +4331,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4347,26 +4351,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -4378,49 +4382,51 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M72" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O72" t="n">
         <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -4435,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -4447,7 +4453,7 @@
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4455,20 +4461,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D74" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -4480,117 +4486,117 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="n">
+        <v>27</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
         <v>2</v>
       </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1</v>
-      </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M75" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4599,19 +4605,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N76" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O76" t="n">
         <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -4619,20 +4625,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D77" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -4644,7 +4650,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4653,19 +4659,19 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P77" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -4673,20 +4679,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -4707,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M78" t="n">
         <v>25</v>
@@ -4716,10 +4722,10 @@
         <v>8</v>
       </c>
       <c r="O78" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -4727,7 +4733,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4746,34 +4752,34 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -4785,13 +4791,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -4815,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
         <v>25</v>
@@ -4824,10 +4830,10 @@
         <v>6</v>
       </c>
       <c r="O80" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P80" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4835,20 +4841,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D81" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4869,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -4881,42 +4887,40 @@
         <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -4925,42 +4929,40 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>-2</v>
+        <v>25</v>
       </c>
       <c r="M82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P82" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4972,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -4981,19 +4983,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -5001,32 +5003,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -5035,43 +5037,45 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N84" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5080,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -5089,19 +5093,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P85" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5109,11 +5113,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -5128,13 +5132,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5146,16 +5150,16 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N86" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P86" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -5163,23 +5167,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -5188,28 +5192,28 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P87" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -5217,23 +5221,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D88" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5251,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -5260,10 +5264,10 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5271,33 +5275,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>2</v>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
@@ -5305,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P89" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5325,53 +5329,53 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
         <v>6</v>
       </c>
-      <c r="D90" t="n">
-        <v>4</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>6</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>8</v>
-      </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5379,20 +5383,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -5404,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -5413,19 +5417,19 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5433,17 +5437,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -5458,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5467,19 +5471,19 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
         <v>8</v>
       </c>
-      <c r="O92" t="n">
-        <v>4</v>
-      </c>
       <c r="P92" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5487,17 +5491,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -5512,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5521,29 +5525,27 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="n">
-        <v>1</v>
-      </c>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -5597,14 +5599,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
@@ -5622,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5631,19 +5633,19 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P95" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
@@ -5653,7 +5655,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5678,13 +5680,13 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -5693,13 +5695,13 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O96" t="n">
         <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5707,47 +5709,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
         <v>6</v>
-      </c>
-      <c r="D97" t="n">
-        <v>7</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>6</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -5761,17 +5763,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -5792,16 +5794,16 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
@@ -5815,7 +5817,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -5846,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -5855,13 +5857,13 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -5869,7 +5871,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tymal Mills</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -5879,7 +5881,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -5903,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -5915,10 +5917,64 @@
         <v>4</v>
       </c>
       <c r="P100" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4</v>
+      </c>
+      <c r="P101" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="n">
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5966,58 +6022,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D3" t="n">
         <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -6027,13 +6083,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
@@ -6042,150 +6098,150 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -6194,299 +6250,299 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
         <v>5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C23" t="n">
+        <v>64</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
         <v>2</v>
-      </c>
-      <c r="C23" t="n">
-        <v>53</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D24" t="n">
         <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
@@ -6498,20 +6554,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -6521,13 +6577,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -6576,10 +6632,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -6604,14 +6660,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6620,7 +6676,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -6636,7 +6692,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -6652,11 +6708,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -6668,7 +6724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6684,7 +6740,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -6700,11 +6756,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -6716,11 +6772,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -6732,7 +6788,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6748,7 +6804,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6764,14 +6820,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -6780,14 +6836,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -6812,7 +6868,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -6828,14 +6884,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6844,14 +6900,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6860,14 +6916,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6876,14 +6932,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -6892,14 +6948,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -6908,14 +6964,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -6924,11 +6980,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
         <v>2</v>
@@ -6940,11 +6996,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
@@ -6956,11 +7012,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>2</v>
@@ -6972,11 +7028,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
@@ -6988,11 +7044,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
         <v>2</v>
@@ -7004,11 +7060,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
@@ -7020,7 +7076,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7040,7 +7096,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
@@ -7060,7 +7116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7372,6 +7428,62 @@
         </is>
       </c>
       <c r="F11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Welsh Fire vs Trent Rockets, 11th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Trent Rockets won by 9 wkts</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MI London vs London Spirit, 12th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>London Spirit won by 7 wkts</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7386,7 +7498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12476,6 +12588,995 @@
         <v>4</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>11</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Philip Salt</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>11</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Craig Overton</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>11</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Matthew Short</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>11</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>11</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>11</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Rachin Ravindra</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>11</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Calvin Harrison</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>11</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>11</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Finn Allen</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>11</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>11</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Sam Billings</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>11</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>11</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>11</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Chris Woakes</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>11</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Mohammad Amir</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>11</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>11</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Lewis Gregory</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>11</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>11</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Tom Banton</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>11</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>11</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Sam Cook</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>12</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>12</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Jonny Bairstow</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>12</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>12</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Peter Willey</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>12</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Nicholas Pooran</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>12</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Sherfane Rutherford</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>12</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>James Coles</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>12</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>12</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Tom Curran</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>12</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>David Willey</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>12</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Adam Milne</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>12</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Adam Zampa</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>12</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Andrew Tye</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>12</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Liam Livingstone</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>12</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>12</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Lhuan-dre Pretorius</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>12</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>12</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Dewald Brevis</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>12</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>12</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Richard Gleeson</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>12</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Olly Stone</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>12</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,32 +515,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -549,23 +549,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>249</v>
+        <v>93</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -627,23 +625,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -661,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -673,7 +671,7 @@
         <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -683,26 +681,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -717,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="M5" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>8</v>
@@ -729,59 +727,57 @@
         <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
@@ -790,149 +786,153 @@
         <v>256</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>159</v>
+        <v>232</v>
       </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>229</v>
+        <v>61</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -941,48 +941,46 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -997,10 +995,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -1009,90 +1007,92 @@
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>133</v>
+      </c>
+      <c r="D11" t="n">
+        <v>95</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>184</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
-        <v>36</v>
-      </c>
-      <c r="D11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>48</v>
-      </c>
-      <c r="M11" t="n">
-        <v>124</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M12" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>8</v>
@@ -1119,32 +1119,34 @@
         <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
-        <v>78</v>
-      </c>
-      <c r="D13" t="n">
-        <v>39</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
@@ -1158,44 +1160,42 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1216,22 +1216,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -1239,27 +1239,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -1273,92 +1273,92 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="N15" t="n">
         <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="M16" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -1367,37 +1367,37 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>136</v>
+      </c>
+      <c r="N17" t="n">
+        <v>18</v>
+      </c>
+      <c r="O17" t="n">
         <v>16</v>
       </c>
-      <c r="M17" t="n">
-        <v>106</v>
-      </c>
-      <c r="N17" t="n">
-        <v>24</v>
-      </c>
-      <c r="O17" t="n">
-        <v>12</v>
-      </c>
       <c r="P17" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1405,23 +1405,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1430,117 +1430,119 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="M19" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1549,45 +1551,43 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>4</v>
@@ -1596,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1605,19 +1605,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M21" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O21" t="n">
         <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1625,23 +1625,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1659,75 +1659,73 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28</v>
+      </c>
+      <c r="M23" t="n">
+        <v>103</v>
+      </c>
+      <c r="N23" t="n">
         <v>6</v>
       </c>
-      <c r="F23" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>128</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8</v>
-      </c>
       <c r="O23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1735,23 +1733,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1760,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1769,40 +1767,42 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1823,19 +1823,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O25" t="n">
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1843,32 +1843,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1877,44 +1877,46 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="M26" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -1928,22 +1930,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -1951,32 +1953,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n">
         <v>6</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1985,19 +1987,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="M28" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2005,32 +2007,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>4</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2039,19 +2041,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2059,23 +2061,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2084,63 +2086,61 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2149,19 +2149,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="N31" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2169,20 +2169,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2225,23 +2225,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2259,19 +2259,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M33" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2279,23 +2279,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>2</v>
-      </c>
-      <c r="C34" t="n">
-        <v>48</v>
-      </c>
-      <c r="D34" t="n">
-        <v>26</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -2304,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2313,102 +2313,102 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="M34" t="n">
         <v>53</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P34" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="M35" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M36" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2435,40 +2435,42 @@
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2477,19 +2479,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2497,17 +2499,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2522,28 +2524,28 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O38" t="n">
         <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
@@ -2553,32 +2555,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2587,19 +2589,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O39" t="n">
         <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -2607,20 +2609,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2632,7 +2634,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2641,46 +2643,48 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M40" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O40" t="n">
         <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2695,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M41" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="N41" t="n">
         <v>8</v>
@@ -2707,7 +2711,7 @@
         <v>12</v>
       </c>
       <c r="P41" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2715,26 +2719,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2749,10 +2753,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>94</v>
+        <v>-2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -2761,11 +2765,9 @@
         <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
         <v>1</v>
       </c>
@@ -2773,26 +2775,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D43" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2804,22 +2806,22 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O43" t="n">
         <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2827,24 +2829,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
         <v>4</v>
       </c>
-      <c r="F44" t="n">
-        <v>3</v>
-      </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
@@ -2852,84 +2854,82 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="D45" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M45" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P45" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2937,18 +2937,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" t="n">
         <v>7</v>
       </c>
-      <c r="D46" t="n">
-        <v>5</v>
-      </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
@@ -2971,73 +2971,75 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D47" t="n">
+        <v>54</v>
+      </c>
+      <c r="E47" t="n">
         <v>6</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>12</v>
       </c>
       <c r="P47" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3045,17 +3047,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -3070,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3079,19 +3081,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
         <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3099,32 +3101,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3133,46 +3135,50 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="M49" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P49" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -3187,10 +3193,10 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N50" t="n">
         <v>8</v>
@@ -3199,7 +3205,7 @@
         <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3207,20 +3213,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D51" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -3241,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3250,36 +3256,36 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D52" t="n">
         <v>29</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -3297,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -3309,25 +3315,27 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -3351,10 +3359,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3363,7 +3371,7 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3371,32 +3379,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -3405,19 +3413,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="N54" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -3425,53 +3433,53 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="C55" t="n">
-        <v>52</v>
-      </c>
-      <c r="D55" t="n">
-        <v>28</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O55" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P55" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3479,53 +3487,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>4</v>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" t="n">
-        <v>55</v>
-      </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N56" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P56" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3533,23 +3541,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D57" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -3558,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3567,19 +3575,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
         <v>12</v>
       </c>
       <c r="P57" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3587,32 +3595,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3621,19 +3629,19 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M58" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
         <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3641,32 +3649,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3675,48 +3683,46 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N59" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>2</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3728,22 +3734,22 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M60" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P60" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3751,53 +3757,53 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D61" t="n">
+        <v>28</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
         <v>5</v>
       </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="M61" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3805,23 +3811,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3830,28 +3836,28 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O62" t="n">
         <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
@@ -3861,26 +3867,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3895,10 +3901,10 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="M63" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -3907,7 +3913,7 @@
         <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3915,53 +3921,53 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
         <v>2</v>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N64" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>12</v>
       </c>
       <c r="P64" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3969,20 +3975,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -4000,22 +4006,22 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M65" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O65" t="n">
         <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -4023,20 +4029,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D66" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -4054,37 +4060,39 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
@@ -4093,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>2</v>
@@ -4111,10 +4119,10 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -4123,7 +4131,7 @@
         <v>12</v>
       </c>
       <c r="P67" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4131,27 +4139,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
         <v>2</v>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
@@ -4165,10 +4173,10 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -4177,42 +4185,40 @@
         <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" t="n">
+        <v>34</v>
+      </c>
+      <c r="D69" t="n">
         <v>19</v>
       </c>
-      <c r="D69" t="n">
-        <v>10</v>
-      </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4221,19 +4227,19 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="M69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P69" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4241,32 +4247,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
         <v>2</v>
       </c>
-      <c r="C70" t="n">
-        <v>23</v>
-      </c>
-      <c r="D70" t="n">
-        <v>14</v>
-      </c>
-      <c r="E70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -4275,54 +4281,52 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N70" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4331,19 +4335,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M71" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4351,53 +4355,53 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>-2</v>
+        <v>27</v>
       </c>
       <c r="M72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="O72" t="n">
         <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
@@ -4407,17 +4411,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -4441,19 +4445,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4461,26 +4465,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -4495,10 +4499,10 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -4507,7 +4511,7 @@
         <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -4515,53 +4519,53 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N75" t="n">
+        <v>14</v>
+      </c>
+      <c r="O75" t="n">
         <v>16</v>
       </c>
-      <c r="O75" t="n">
-        <v>12</v>
-      </c>
       <c r="P75" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
@@ -4571,32 +4575,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4605,19 +4609,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -4625,86 +4629,88 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D77" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
         <v>30</v>
       </c>
-      <c r="E77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>53</v>
-      </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P77" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4713,19 +4719,19 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M78" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -4733,7 +4739,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -4758,13 +4764,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -4773,13 +4779,13 @@
         <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -4787,53 +4793,53 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="M80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>12</v>
       </c>
       <c r="P80" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4841,53 +4847,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>10</v>
+      </c>
+      <c r="M81" t="n">
+        <v>25</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8</v>
+      </c>
+      <c r="O81" t="n">
         <v>12</v>
       </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>22</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>16</v>
-      </c>
-      <c r="O81" t="n">
-        <v>8</v>
-      </c>
       <c r="P81" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -4895,20 +4901,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
+        <v>31</v>
+      </c>
+      <c r="D82" t="n">
         <v>24</v>
       </c>
-      <c r="D82" t="n">
-        <v>26</v>
-      </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -4929,7 +4935,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -4938,10 +4944,10 @@
         <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4949,7 +4955,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -4968,34 +4974,34 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N83" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -5003,17 +5009,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -5034,45 +5040,43 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="M84" t="n">
         <v>25</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O84" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P84" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -5093,7 +5097,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -5102,10 +5106,10 @@
         <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5113,32 +5117,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5147,19 +5151,19 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P86" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -5167,26 +5171,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
         <v>2</v>
       </c>
-      <c r="C87" t="n">
-        <v>10</v>
-      </c>
-      <c r="D87" t="n">
-        <v>8</v>
-      </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -5201,43 +5205,45 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N87" t="n">
         <v>8</v>
       </c>
       <c r="O87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -5246,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -5255,19 +5261,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5275,11 +5281,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -5294,13 +5300,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5312,16 +5318,16 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N89" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5329,14 +5335,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>5</v>
@@ -5354,28 +5360,28 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O90" t="n">
         <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5383,17 +5389,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D91" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -5417,7 +5423,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -5429,7 +5435,7 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5437,23 +5443,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -5471,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -5480,10 +5486,10 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5491,17 +5497,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -5516,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5525,19 +5531,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
+        <v>16</v>
+      </c>
+      <c r="O93" t="n">
         <v>8</v>
       </c>
-      <c r="O93" t="n">
-        <v>4</v>
-      </c>
       <c r="P93" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5545,17 +5551,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -5570,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5579,19 +5585,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
         <v>8</v>
       </c>
-      <c r="O94" t="n">
-        <v>4</v>
-      </c>
       <c r="P94" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -5599,17 +5605,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -5624,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5633,39 +5639,37 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="n">
-        <v>1</v>
-      </c>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -5680,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -5689,19 +5693,19 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
         <v>8</v>
       </c>
-      <c r="O96" t="n">
-        <v>4</v>
-      </c>
       <c r="P96" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5709,7 +5713,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -5734,13 +5738,13 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -5749,13 +5753,13 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -5763,17 +5767,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -5788,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -5797,19 +5801,19 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -5871,7 +5875,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -5902,7 +5906,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -5911,13 +5915,13 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O100" t="n">
         <v>4</v>
       </c>
       <c r="P100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -5925,7 +5929,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tymal Mills</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -5935,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -5959,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -5971,10 +5975,64 @@
         <v>4</v>
       </c>
       <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="n">
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6231,17 +6289,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -6250,17 +6308,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -6269,17 +6327,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -6288,36 +6346,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
@@ -6330,13 +6388,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>5</v>
@@ -6345,55 +6403,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
@@ -6402,74 +6460,74 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -6478,90 +6536,90 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D29" t="n">
         <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D30" t="n">
         <v>1</v>
@@ -6573,20 +6631,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6644,14 +6702,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6660,11 +6718,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
         <v>5</v>
@@ -6676,14 +6734,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6692,14 +6750,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6708,14 +6766,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6724,7 +6782,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6740,11 +6798,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
@@ -6756,11 +6814,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
@@ -6772,7 +6830,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -6804,7 +6862,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6820,11 +6878,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -6836,7 +6894,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6852,14 +6910,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -6868,14 +6926,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6884,7 +6942,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -6900,11 +6958,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>3</v>
@@ -6916,7 +6974,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -6932,7 +6990,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -6948,11 +7006,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -6964,11 +7022,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -6980,14 +7038,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -6996,14 +7054,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -7012,14 +7070,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -7028,14 +7086,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -7044,7 +7102,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7060,11 +7118,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
         <v>2</v>
@@ -7092,7 +7150,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7116,7 +7174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7484,6 +7542,34 @@
         </is>
       </c>
       <c r="F13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Southern Brave vs Birmingham Phoenix, 13th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Southern Brave won by 12 runs</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7498,7 +7584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E264"/>
+  <dimension ref="A1:E286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13577,6 +13663,512 @@
         <v>4</v>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>13</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>13</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Mitchell Owen</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>13</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>13</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Donovan Ferreira</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>13</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Tom Abell</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>13</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Joe Clarke</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>13</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>13</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>13</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>13</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>13</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Scott Currie</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>13</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>13</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Laurie Evans</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>13</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Saif Zaib</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>13</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>13</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>13</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Ben Dwarshuis</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>13</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Usman Tariq</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>13</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Rehan Ahmed</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>13</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Will Smeed</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>13</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>13</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Sean Dickson</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -515,26 +515,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>224</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -543,83 +543,83 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>93</v>
+        <v>312</v>
       </c>
       <c r="M2" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>282</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>340</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M3" t="n">
         <v>177</v>
       </c>
-      <c r="M3" t="n">
-        <v>58</v>
-      </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -681,82 +681,82 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
         <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -771,22 +771,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="M6" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -795,47 +795,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="D7" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -844,39 +844,41 @@
         <v>256</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -885,108 +887,112 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="M8" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>229</v>
+        <v>61</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -995,54 +1001,52 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1051,49 +1055,49 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P11" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>7</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -1107,152 +1111,150 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="N12" t="n">
         <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P12" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N13" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>177</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="M14" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O14" t="n">
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>177</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1264,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1273,19 +1275,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -1293,24 +1295,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
         <v>8</v>
       </c>
-      <c r="F16" t="n">
-        <v>5</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
@@ -1318,86 +1320,84 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
+        <v>29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="N17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1405,23 +1405,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1433,13 +1433,13 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -1448,137 +1448,139 @@
         <v>36</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>177</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>149</v>
+      </c>
+      <c r="N19" t="n">
         <v>12</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>144</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="M20" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -1587,37 +1589,37 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>136</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18</v>
+      </c>
+      <c r="O21" t="n">
         <v>16</v>
       </c>
-      <c r="M21" t="n">
-        <v>106</v>
-      </c>
-      <c r="N21" t="n">
-        <v>24</v>
-      </c>
-      <c r="O21" t="n">
-        <v>12</v>
-      </c>
       <c r="P21" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -1625,23 +1627,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1656,22 +1658,22 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O22" t="n">
         <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1679,77 +1681,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="M23" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1758,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1767,45 +1771,47 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>4</v>
@@ -1814,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1823,19 +1829,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M25" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N25" t="n">
+        <v>24</v>
+      </c>
+      <c r="O25" t="n">
         <v>16</v>
       </c>
-      <c r="O25" t="n">
-        <v>12</v>
-      </c>
       <c r="P25" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1843,32 +1849,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1877,45 +1883,43 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1924,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1933,19 +1937,19 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -1953,23 +1957,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
         <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1978,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1987,40 +1991,42 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -2038,22 +2044,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M29" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2061,32 +2067,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2095,19 +2101,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N30" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -2115,32 +2121,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2149,19 +2155,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="M31" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2169,24 +2175,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="n">
-        <v>4</v>
-      </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
@@ -2194,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2203,45 +2209,43 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O32" t="n">
         <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>141</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -2250,7 +2254,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2259,19 +2263,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2279,32 +2283,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2313,19 +2317,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="M34" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P34" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2333,23 +2337,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2358,63 +2362,63 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>137</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2423,23 +2427,21 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -2449,7 +2451,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -2488,10 +2490,10 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P37" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2499,55 +2501,57 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="D38" t="n">
+        <v>51</v>
+      </c>
+      <c r="E38" t="n">
         <v>9</v>
       </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="M38" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
@@ -2555,56 +2559,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="N39" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
         <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2993,32 +2999,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3027,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P47" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -3047,53 +3053,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="M48" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O48" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3101,32 +3107,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3135,56 +3141,52 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3193,19 +3195,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M50" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O50" t="n">
         <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3213,23 +3215,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D51" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -3247,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3256,39 +3258,37 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P51" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -3303,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N52" t="n">
         <v>8</v>
@@ -3315,36 +3315,34 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3359,10 +3357,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="M53" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3371,34 +3369,38 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>97</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -3413,100 +3415,104 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="M54" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D55" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>12</v>
       </c>
       <c r="P55" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -3521,19 +3527,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="M56" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3541,32 +3547,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="D57" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3575,19 +3581,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
         <v>8</v>
       </c>
-      <c r="O57" t="n">
-        <v>12</v>
-      </c>
       <c r="P57" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3595,53 +3601,53 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O58" t="n">
         <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3649,17 +3655,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -3683,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -3695,7 +3701,7 @@
         <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3703,32 +3709,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3737,19 +3743,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="M60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P60" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3757,17 +3763,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -3791,7 +3797,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3800,10 +3806,10 @@
         <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3811,32 +3817,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3845,54 +3851,52 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>16</v>
       </c>
-      <c r="O62" t="n">
-        <v>12</v>
-      </c>
       <c r="P62" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3901,19 +3905,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P63" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -3921,32 +3925,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3955,19 +3959,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M64" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3975,136 +3979,136 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D65" t="n">
+        <v>20</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
         <v>5</v>
       </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="M65" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O65" t="n">
         <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N66" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -4119,10 +4123,10 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="M67" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -4131,7 +4135,7 @@
         <v>12</v>
       </c>
       <c r="P67" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4139,20 +4143,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -4173,19 +4177,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P68" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4193,32 +4197,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>3</v>
       </c>
       <c r="C69" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
         <v>2</v>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4227,19 +4231,19 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N69" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O69" t="n">
         <v>12</v>
       </c>
       <c r="P69" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4247,86 +4251,88 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="M70" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
         <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D71" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4335,19 +4341,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4355,32 +4361,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>2</v>
       </c>
-      <c r="C72" t="n">
-        <v>23</v>
-      </c>
-      <c r="D72" t="n">
-        <v>14</v>
-      </c>
-      <c r="E72" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4389,54 +4395,52 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N72" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P72" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4445,19 +4449,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M73" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
         <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4465,32 +4469,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4499,37 +4503,39 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="M74" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O74" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -4538,63 +4544,61 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -4609,10 +4613,10 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -4621,7 +4625,7 @@
         <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -4629,53 +4633,53 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N77" t="n">
+        <v>14</v>
+      </c>
+      <c r="O77" t="n">
         <v>16</v>
       </c>
-      <c r="O77" t="n">
-        <v>12</v>
-      </c>
       <c r="P77" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
@@ -4685,86 +4689,88 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
+        <v>22</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
         <v>30</v>
       </c>
-      <c r="E78" t="n">
-        <v>5</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>53</v>
-      </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4773,16 +4779,16 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P79" t="n">
         <v>57</v>
@@ -4793,32 +4799,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4827,16 +4833,16 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N80" t="n">
+        <v>24</v>
+      </c>
+      <c r="O80" t="n">
         <v>8</v>
-      </c>
-      <c r="O80" t="n">
-        <v>12</v>
       </c>
       <c r="P80" t="n">
         <v>57</v>
@@ -4847,32 +4853,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4881,19 +4887,19 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P81" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -4901,26 +4907,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4935,19 +4941,19 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N82" t="n">
         <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P82" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4955,26 +4961,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4986,22 +4992,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M83" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -5063,53 +5069,53 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5281,17 +5287,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -5300,13 +5306,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5315,19 +5321,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M89" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P89" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5389,26 +5395,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -5423,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5435,7 +5441,7 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5443,23 +5449,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D92" t="n">
         <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -5477,7 +5483,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -5489,7 +5495,7 @@
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5497,23 +5503,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -5522,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5531,19 +5537,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5551,17 +5557,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -5576,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5585,19 +5591,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -6080,74 +6086,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
@@ -6156,169 +6162,169 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -6327,17 +6333,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>4</v>
@@ -6369,7 +6375,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>90</v>
@@ -6384,93 +6390,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
@@ -6536,39 +6542,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D26" t="n">
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -6593,58 +6599,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6702,14 +6708,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6718,14 +6724,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6734,11 +6740,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
@@ -6750,11 +6756,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -6766,7 +6772,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6782,14 +6788,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6798,14 +6804,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6814,7 +6820,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -6830,11 +6836,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
@@ -6846,11 +6852,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
@@ -6862,11 +6868,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
@@ -6878,11 +6884,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -6910,11 +6916,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -6926,11 +6932,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
@@ -6942,14 +6948,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6958,14 +6964,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6990,11 +6996,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
         <v>3</v>
@@ -7006,11 +7012,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
         <v>3</v>
@@ -7022,11 +7028,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -7042,7 +7048,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
         <v>3</v>
@@ -7054,7 +7060,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7070,11 +7076,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
         <v>3</v>
@@ -7086,11 +7092,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>3</v>
@@ -7102,14 +7108,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -7118,7 +7124,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -7134,7 +7140,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7150,11 +7156,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>2</v>
@@ -7174,7 +7180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7570,6 +7576,34 @@
         </is>
       </c>
       <c r="F14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Manchester Super Giants vs Trent Rockets, 14th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Trent Rockets won by 6 wkts</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7584,7 +7618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E286"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14169,6 +14203,489 @@
         <v>29</v>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>14</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>14</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Lewis Gregory</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>14</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>14</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>14</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Jos Buttler</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>14</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Heinrich Klaasen</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>14</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Finn Allen</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>14</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Leus du Plooy</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>14</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Mohammad Amir</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>14</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Craig Overton</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>14</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>14</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Calvin Harrison</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>14</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>14</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>14</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Gus Atkinson</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>14</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Tom Banton</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>14</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Sam Billings</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>14</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Sonny Baker</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>14</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Josh Tongue</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>14</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Liam Dawson</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>14</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,26 +515,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -543,185 +543,185 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>312</v>
+        <v>96</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>224</v>
+      </c>
+      <c r="D3" t="n">
+        <v>131</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>312</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D3" t="n">
-        <v>51</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M3" t="n">
-        <v>177</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>12</v>
-      </c>
-      <c r="P3" t="n">
-        <v>282</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>145</v>
+      </c>
+      <c r="D4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>173</v>
-      </c>
-      <c r="D4" t="n">
-        <v>87</v>
-      </c>
-      <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" t="n">
-        <v>14</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="M5" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>12</v>
@@ -730,7 +730,7 @@
         <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
@@ -795,26 +795,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -829,23 +829,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="N7" t="n">
         <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
         <v>256</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>1</v>
       </c>
@@ -853,53 +851,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -915,13 +913,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" t="n">
         <v>9</v>
@@ -945,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M9" t="n">
         <v>61</v>
@@ -954,10 +952,10 @@
         <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -967,86 +965,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="M10" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
         <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1055,33 +1057,31 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1102,28 +1102,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1131,26 +1131,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1162,22 +1162,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="M13" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -1185,32 +1185,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1219,108 +1219,108 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
+        <v>130</v>
+      </c>
+      <c r="D15" t="n">
+        <v>83</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="M15" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O15" t="n">
         <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1329,54 +1329,52 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1385,40 +1383,42 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="M17" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>182</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -1430,51 +1430,49 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>177</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1486,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M19" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -1515,245 +1513,243 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="M21" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>16</v>
       </c>
       <c r="P21" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
         <v>5</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>116</v>
-      </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="N22" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
+        <v>38</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>42</v>
+      </c>
+      <c r="M23" t="n">
         <v>108</v>
       </c>
-      <c r="D23" t="n">
-        <v>72</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>144</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1762,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1771,56 +1767,52 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1829,19 +1821,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="M25" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N25" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1849,23 +1841,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D26" t="n">
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
@@ -1874,28 +1866,28 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M26" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -1903,23 +1895,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1931,52 +1923,56 @@
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1988,51 +1984,49 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2044,55 +2038,57 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="M29" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2101,43 +2097,45 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="M30" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>149</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2155,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2164,34 +2162,38 @@
         <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P31" t="n">
-        <v>148</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -2200,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2209,43 +2211,45 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P32" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>166</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -2254,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2263,19 +2267,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M33" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P33" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2283,32 +2287,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2317,19 +2321,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N34" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O34" t="n">
         <v>16</v>
       </c>
       <c r="P34" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2337,88 +2341,86 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
-        <v>94</v>
-      </c>
-      <c r="D35" t="n">
-        <v>64</v>
-      </c>
-      <c r="E35" t="n">
-        <v>7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
-        <v>141</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2427,37 +2429,41 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="M36" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -2466,34 +2472,34 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O37" t="n">
         <v>16</v>
       </c>
       <c r="P37" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2501,26 +2507,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2532,80 +2538,76 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>31</v>
+      </c>
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="n">
-        <v>9</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>4</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="M39" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="N39" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
@@ -2615,32 +2617,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2649,54 +2651,52 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="M40" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2705,40 +2705,42 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>124</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2759,75 +2761,73 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>-2</v>
+        <v>17</v>
       </c>
       <c r="M42" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P42" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>69</v>
+      </c>
+      <c r="D43" t="n">
+        <v>58</v>
+      </c>
+      <c r="E43" t="n">
         <v>3</v>
       </c>
-      <c r="C43" t="n">
-        <v>26</v>
-      </c>
-      <c r="D43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
       <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>3</v>
       </c>
-      <c r="G43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="M43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O43" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P43" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2835,23 +2835,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D44" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2866,22 +2866,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -2889,53 +2889,53 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="M45" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>16</v>
       </c>
       <c r="P45" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2943,88 +2943,86 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>106</v>
+      </c>
+      <c r="N46" t="n">
         <v>12</v>
-      </c>
-      <c r="D46" t="n">
-        <v>7</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>12</v>
-      </c>
-      <c r="M46" t="n">
-        <v>83</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3033,73 +3031,77 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M47" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>16</v>
       </c>
       <c r="P47" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N48" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3107,33 +3109,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="D49" t="n">
+        <v>43</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
       <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>3</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
@@ -3141,19 +3143,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="M49" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
         <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3161,32 +3163,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3195,19 +3197,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N50" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P50" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -3215,80 +3217,82 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O51" t="n">
         <v>12</v>
       </c>
       <c r="P51" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -3303,10 +3307,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="M52" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="N52" t="n">
         <v>8</v>
@@ -3315,7 +3319,7 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3323,26 +3327,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -3357,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>94</v>
+        <v>-2</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -3369,11 +3373,9 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
         <v>1</v>
       </c>
@@ -3381,27 +3383,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
         <v>3</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
@@ -3415,19 +3417,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
+        <v>12</v>
+      </c>
+      <c r="M54" t="n">
         <v>83</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P54" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
@@ -3437,27 +3439,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>3</v>
       </c>
-      <c r="C55" t="n">
-        <v>53</v>
-      </c>
-      <c r="D55" t="n">
-        <v>29</v>
-      </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
@@ -3471,75 +3473,73 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N55" t="n">
         <v>8</v>
       </c>
       <c r="O55" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P55" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86</v>
+      </c>
+      <c r="N56" t="n">
         <v>8</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>80</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -3547,53 +3547,53 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>60</v>
+      </c>
+      <c r="D57" t="n">
+        <v>38</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="C57" t="n">
-        <v>7</v>
-      </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="M57" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O57" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P57" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3601,53 +3601,53 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
         <v>3</v>
       </c>
-      <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>6</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3</v>
-      </c>
       <c r="M58" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N58" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3655,17 +3655,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -3689,43 +3689,45 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="M59" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3734,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3743,19 +3745,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>12</v>
       </c>
       <c r="P60" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3763,23 +3765,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D61" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -3788,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3803,13 +3805,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
         <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3817,7 +3819,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -3842,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3854,16 +3856,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
         <v>16</v>
       </c>
       <c r="P62" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3871,32 +3873,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3905,97 +3907,103 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="M63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B64" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" t="n">
+        <v>66</v>
+      </c>
+      <c r="D64" t="n">
+        <v>44</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>81</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>20</v>
+      </c>
+      <c r="P64" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="n">
         <v>2</v>
       </c>
-      <c r="C64" t="n">
-        <v>52</v>
-      </c>
-      <c r="D64" t="n">
-        <v>28</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" t="n">
-        <v>5</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>68</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>8</v>
-      </c>
-      <c r="O64" t="n">
-        <v>8</v>
-      </c>
-      <c r="P64" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -4004,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -4013,48 +4021,48 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O65" t="n">
         <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -4069,10 +4077,10 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -4081,31 +4089,33 @@
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D67" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -4123,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -4132,10 +4142,10 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P67" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4143,27 +4153,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
@@ -4177,19 +4187,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4197,32 +4207,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4231,103 +4241,103 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="M69" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D70" t="n">
         <v>30</v>
       </c>
       <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>72</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
         <v>8</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" t="n">
-        <v>51</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>14</v>
       </c>
       <c r="O70" t="n">
         <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
         <v>3</v>
       </c>
-      <c r="C71" t="n">
-        <v>11</v>
-      </c>
-      <c r="D71" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>2</v>
-      </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
@@ -4341,19 +4351,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P71" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4361,23 +4371,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
@@ -4386,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -4395,19 +4405,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P72" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -4415,24 +4425,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D73" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
         <v>5</v>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
@@ -4449,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -4458,10 +4468,10 @@
         <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4469,89 +4479,87 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
         <v>2</v>
       </c>
-      <c r="C74" t="n">
-        <v>23</v>
-      </c>
-      <c r="D74" t="n">
-        <v>14</v>
-      </c>
-      <c r="E74" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N74" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P74" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
         <v>2</v>
       </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
@@ -4559,37 +4567,39 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M75" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O75" t="n">
         <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -4604,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4613,37 +4623,39 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>58</v>
+      </c>
+      <c r="N76" t="n">
+        <v>8</v>
+      </c>
+      <c r="O76" t="n">
+        <v>16</v>
+      </c>
+      <c r="P76" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="n">
         <v>2</v>
       </c>
-      <c r="M76" t="n">
-        <v>53</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>12</v>
-      </c>
-      <c r="P76" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -4652,69 +4664,67 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="N77" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>16</v>
       </c>
       <c r="P77" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4723,24 +4733,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N78" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4749,19 +4757,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -4779,7 +4787,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -4788,10 +4796,10 @@
         <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P79" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -4799,32 +4807,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>9</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
         <v>2</v>
       </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4833,19 +4841,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N80" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P80" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4853,80 +4861,82 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D81" t="n">
+        <v>22</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
         <v>30</v>
       </c>
-      <c r="E81" t="n">
-        <v>5</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>53</v>
-      </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P81" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4941,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="M82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>8</v>
@@ -4953,7 +4963,7 @@
         <v>12</v>
       </c>
       <c r="P82" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4961,53 +4971,53 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>25</v>
+      </c>
+      <c r="N83" t="n">
         <v>24</v>
-      </c>
-      <c r="E83" t="n">
-        <v>5</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>36</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>8</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -5015,26 +5025,26 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5046,22 +5056,22 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="M84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P84" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -5069,53 +5079,53 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="n">
+        <v>24</v>
+      </c>
+      <c r="D85" t="n">
+        <v>26</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>2</v>
       </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
-      </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P85" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5123,17 +5133,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -5142,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -5157,10 +5167,10 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="n">
         <v>25</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
       </c>
       <c r="N86" t="n">
         <v>8</v>
@@ -5169,7 +5179,7 @@
         <v>12</v>
       </c>
       <c r="P86" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -5177,17 +5187,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -5208,57 +5218,55 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>25</v>
       </c>
       <c r="N87" t="n">
+        <v>14</v>
+      </c>
+      <c r="O87" t="n">
         <v>8</v>
       </c>
-      <c r="O87" t="n">
-        <v>12</v>
-      </c>
       <c r="P87" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="n">
-        <v>2</v>
-      </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -5267,19 +5275,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N88" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5287,17 +5295,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -5312,7 +5320,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5321,19 +5329,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
+        <v>32</v>
+      </c>
+      <c r="O89" t="n">
         <v>8</v>
       </c>
-      <c r="O89" t="n">
-        <v>12</v>
-      </c>
       <c r="P89" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5341,17 +5349,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5366,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -5375,19 +5383,19 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
         <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5449,33 +5457,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>2</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
@@ -5483,19 +5491,19 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P92" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5503,23 +5511,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D93" t="n">
         <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -5537,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -5549,7 +5557,7 @@
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5557,23 +5565,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -5582,7 +5590,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5591,19 +5599,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -5611,17 +5619,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -5636,7 +5644,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5645,19 +5653,19 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
+        <v>16</v>
+      </c>
+      <c r="O95" t="n">
         <v>8</v>
       </c>
-      <c r="O95" t="n">
-        <v>4</v>
-      </c>
       <c r="P95" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -5665,17 +5673,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -5696,22 +5704,22 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O96" t="n">
         <v>8</v>
       </c>
       <c r="P96" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5719,17 +5727,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Moeen Ali</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -5753,7 +5761,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -5765,7 +5773,7 @@
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -5773,11 +5781,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -5798,13 +5806,13 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -5813,13 +5821,13 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
+        <v>12</v>
+      </c>
+      <c r="O98" t="n">
         <v>8</v>
       </c>
-      <c r="O98" t="n">
-        <v>4</v>
-      </c>
       <c r="P98" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -5827,17 +5835,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -5852,28 +5860,28 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -5881,17 +5889,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -5912,22 +5920,22 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P100" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -5935,17 +5943,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Tom Kohler-Cadmore</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -5960,7 +5968,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5969,19 +5977,19 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O101" t="n">
         <v>4</v>
       </c>
       <c r="P101" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -5989,56 +5997,218 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>Ed Barnard</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>8</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" t="n">
+        <v>4</v>
+      </c>
+      <c r="P103" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>4</v>
+      </c>
+      <c r="P104" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
         <v>-2</v>
       </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>4</v>
-      </c>
-      <c r="P102" t="n">
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>4</v>
+      </c>
+      <c r="P105" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="n">
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6166,10 +6336,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -6219,17 +6389,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
@@ -6238,153 +6408,153 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
         <v>6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -6394,13 +6564,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -6409,112 +6579,112 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="D23" t="n">
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
@@ -6523,134 +6693,134 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" t="n">
+        <v>73</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
         <v>3</v>
-      </c>
-      <c r="C29" t="n">
-        <v>64</v>
-      </c>
-      <c r="D29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
         <v>6</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6692,14 +6862,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -6708,14 +6878,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6724,14 +6894,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -6740,14 +6910,14 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -6756,14 +6926,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6772,7 +6942,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -6788,11 +6958,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
@@ -6820,14 +6990,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -6836,14 +7006,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -6852,7 +7022,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -6868,7 +7038,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6884,11 +7054,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
@@ -6900,7 +7070,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -6916,7 +7086,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -6948,11 +7118,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
         <v>4</v>
@@ -6964,11 +7134,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
@@ -6980,14 +7150,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -6996,14 +7166,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -7012,14 +7182,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -7028,11 +7198,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -7044,7 +7214,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -7060,11 +7230,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>3</v>
@@ -7076,7 +7246,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7092,7 +7262,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -7108,11 +7278,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
         <v>3</v>
@@ -7124,14 +7294,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -7140,14 +7310,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -7156,14 +7326,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -7180,7 +7350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7604,6 +7774,62 @@
         </is>
       </c>
       <c r="F15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Birmingham Phoenix vs Welsh Fire, 15th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Welsh Fire won by 7 wkts</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>London Spirit vs Southern Brave, 16th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Southern Brave won by 5 wkts</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7618,7 +7844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14686,6 +14912,1041 @@
         <v>4</v>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>15</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Mitchell Owen</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>15</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>15</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Will Smeed</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>15</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Sam Cook</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>15</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Joe Clarke</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>15</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Rehan Ahmed</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>15</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>15</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>15</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Laurie Evans</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>15</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Chris Woakes</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>15</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>15</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Donovan Ferreira</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>15</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Tom Kohler-Cadmore</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>15</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Sean Dickson</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>15</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Rachin Ravindra</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>15</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Scott Currie</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>15</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>15</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Chris Wood</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>15</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>15</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>15</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Usman Tariq</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>15</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Philip Salt</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>16</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Lhuan-dre Pretorius</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>16</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>16</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Jonny Bairstow</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>16</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>16</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>16</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>16</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Liam Livingstone</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>16</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>16</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Dewald Brevis</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>16</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>James Coles</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>16</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Moeen Ali</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>16</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>16</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Nikhil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>16</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>David Willey</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>16</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>16</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Andrew Tye</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>16</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>16</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Adam Milne</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>16</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Adam Zampa</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>16</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>16</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>16</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>16</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Willey</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,23 +569,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D3" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -594,166 +594,168 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="D4" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>314</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P4" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>184</v>
-      </c>
-      <c r="M4" t="n">
-        <v>83</v>
-      </c>
-      <c r="N4" t="n">
-        <v>30</v>
-      </c>
-      <c r="O4" t="n">
-        <v>16</v>
-      </c>
-      <c r="P4" t="n">
-        <v>313</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>195</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>276</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>52</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>173</v>
-      </c>
-      <c r="D5" t="n">
-        <v>87</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>249</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>12</v>
-      </c>
-      <c r="P5" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -771,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -783,70 +785,68 @@
         <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>256</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -855,29 +855,29 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>113</v>
+      </c>
+      <c r="D8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" t="n">
-        <v>69</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
@@ -885,19 +885,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="M8" t="n">
         <v>114</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -909,112 +909,110 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>9</v>
       </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>61</v>
+        <v>254</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>191</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>56</v>
+      </c>
+      <c r="O10" t="n">
         <v>20</v>
       </c>
-      <c r="F10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>205</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>16</v>
-      </c>
       <c r="P10" t="n">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -1023,32 +1021,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1057,19 +1055,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1077,17 +1075,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1102,7 +1100,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1111,19 +1109,19 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O12" t="n">
         <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -1131,20 +1129,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
@@ -1156,55 +1154,59 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="O13" t="n">
         <v>20</v>
       </c>
       <c r="P13" t="n">
-        <v>237</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1219,10 +1221,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M14" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="N14" t="n">
         <v>8</v>
@@ -1231,61 +1233,63 @@
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N15" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1299,7 +1303,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -1314,7 +1318,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1332,16 +1336,16 @@
         <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="N16" t="n">
         <v>44</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1349,63 +1353,61 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="N17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1415,13 +1417,13 @@
         <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1436,22 +1438,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="O18" t="n">
         <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -1459,107 +1461,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
+        <v>130</v>
+      </c>
+      <c r="D19" t="n">
+        <v>83</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="M19" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>6</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M20" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1567,32 +1571,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1601,54 +1605,52 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1657,54 +1659,52 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="M22" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1713,19 +1713,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1733,20 +1733,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>5</v>
       </c>
       <c r="C24" t="n">
+        <v>124</v>
+      </c>
+      <c r="D24" t="n">
         <v>102</v>
       </c>
-      <c r="D24" t="n">
-        <v>84</v>
-      </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1767,19 +1767,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O24" t="n">
         <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -1787,53 +1787,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1841,78 +1841,82 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="M26" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>174</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
         <v>8</v>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -1920,35 +1924,33 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1957,7 +1959,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1972,7 +1974,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1990,16 +1992,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="N28" t="n">
         <v>18</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -2007,58 +2009,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2067,19 +2069,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2097,7 +2099,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2106,10 +2108,10 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2119,23 +2121,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -2153,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2162,47 +2164,45 @@
         <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2211,75 +2211,73 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
+        <v>102</v>
+      </c>
+      <c r="D33" t="n">
+        <v>84</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>127</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32</v>
+      </c>
+      <c r="O33" t="n">
         <v>20</v>
       </c>
-      <c r="D33" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>23</v>
-      </c>
-      <c r="M33" t="n">
-        <v>108</v>
-      </c>
-      <c r="N33" t="n">
-        <v>16</v>
-      </c>
-      <c r="O33" t="n">
-        <v>16</v>
-      </c>
       <c r="P33" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -2287,32 +2285,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2321,19 +2319,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="M34" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N34" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>16</v>
       </c>
       <c r="P34" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2341,23 +2339,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
@@ -2366,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2375,19 +2373,19 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="M35" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N35" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="O35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P35" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -2395,23 +2393,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2420,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2429,77 +2427,75 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P36" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4</v>
-      </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="N37" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="O37" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P37" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -2507,86 +2503,88 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="E38" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="M38" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
         <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>166</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2595,19 +2593,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>35</v>
+        <v>-2</v>
       </c>
       <c r="M39" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="N39" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
         <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
@@ -2617,32 +2615,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2651,19 +2649,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -2671,26 +2669,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2705,10 +2703,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -2717,42 +2715,40 @@
         <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2761,19 +2757,19 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P42" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -2781,53 +2777,53 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>3</v>
       </c>
-      <c r="F43" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N43" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P43" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2835,23 +2831,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2860,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2869,40 +2865,44 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D45" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2932,43 +2932,47 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P45" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2977,19 +2981,19 @@
         <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="N46" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="O46" t="n">
         <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -2997,23 +3001,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -3022,7 +3026,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3031,56 +3035,52 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
         <v>16</v>
       </c>
       <c r="P47" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3089,43 +3089,45 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="M48" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O48" t="n">
         <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3143,7 +3145,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -3155,7 +3157,7 @@
         <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3163,26 +3165,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -3197,10 +3199,10 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="M50" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3209,34 +3211,36 @@
         <v>16</v>
       </c>
       <c r="P50" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -3248,78 +3252,76 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="M51" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>69</v>
+      </c>
+      <c r="D52" t="n">
+        <v>58</v>
+      </c>
+      <c r="E52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="n">
-        <v>64</v>
-      </c>
-      <c r="D52" t="n">
-        <v>50</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>6</v>
       </c>
-      <c r="F52" t="n">
-        <v>2</v>
-      </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M52" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O52" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P52" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -3327,20 +3329,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -3361,48 +3363,46 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P53" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="n">
+        <v>104</v>
+      </c>
+      <c r="D54" t="n">
+        <v>92</v>
+      </c>
+      <c r="E54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" t="n">
-        <v>12</v>
-      </c>
-      <c r="D54" t="n">
-        <v>7</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -3417,54 +3417,52 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="M54" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3473,19 +3471,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="M55" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O55" t="n">
         <v>16</v>
       </c>
       <c r="P55" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3493,32 +3491,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3527,73 +3525,77 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M56" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>2</v>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
       <c r="L57" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N57" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O57" t="n">
         <v>16</v>
       </c>
       <c r="P57" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3601,33 +3603,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="D58" t="n">
+        <v>43</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
         <v>5</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>3</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
@@ -3635,19 +3637,19 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="M58" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O58" t="n">
         <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3655,26 +3657,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3689,10 +3691,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -3701,34 +3703,32 @@
         <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>69</v>
+      </c>
+      <c r="D60" t="n">
+        <v>46</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="C60" t="n">
-        <v>75</v>
-      </c>
-      <c r="D60" t="n">
-        <v>54</v>
-      </c>
-      <c r="E60" t="n">
-        <v>6</v>
-      </c>
-      <c r="F60" t="n">
-        <v>5</v>
-      </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
@@ -3736,28 +3736,28 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O60" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -3765,80 +3765,82 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
         <v>2</v>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>72</v>
-      </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N61" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O61" t="n">
         <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3853,19 +3855,19 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M62" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="N62" t="n">
         <v>8</v>
       </c>
       <c r="O62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3873,17 +3875,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D63" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E63" t="n">
         <v>6</v>
@@ -3898,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3913,45 +3915,43 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P63" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>5</v>
       </c>
       <c r="C64" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="D64" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
         <v>3</v>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
@@ -3965,10 +3965,10 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -3977,37 +3977,37 @@
         <v>20</v>
       </c>
       <c r="P64" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
         <v>3</v>
       </c>
-      <c r="C65" t="n">
-        <v>53</v>
-      </c>
-      <c r="D65" t="n">
-        <v>29</v>
-      </c>
-      <c r="E65" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" t="n">
-        <v>3</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
@@ -4021,45 +4021,43 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N65" t="n">
         <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P65" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>3</v>
@@ -4068,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -4077,75 +4075,73 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P66" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>86</v>
+      </c>
+      <c r="N67" t="n">
         <v>8</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>80</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>16</v>
       </c>
       <c r="P67" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4153,23 +4149,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="n">
         <v>3</v>
       </c>
-      <c r="C68" t="n">
-        <v>4</v>
-      </c>
-      <c r="D68" t="n">
-        <v>5</v>
-      </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>3</v>
@@ -4187,19 +4183,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M68" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P68" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -4207,23 +4203,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D69" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -4232,28 +4228,28 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
@@ -4263,32 +4259,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
         <v>3</v>
       </c>
-      <c r="C70" t="n">
-        <v>53</v>
-      </c>
-      <c r="D70" t="n">
-        <v>30</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>7</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -4297,27 +4293,29 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>72</v>
+        <v>-2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P70" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -4342,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -4354,16 +4352,16 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>16</v>
       </c>
       <c r="P71" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4371,56 +4369,58 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>81</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>20</v>
+      </c>
+      <c r="P72" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
         <v>2</v>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>4</v>
-      </c>
-      <c r="M72" t="n">
-        <v>50</v>
-      </c>
-      <c r="N72" t="n">
-        <v>16</v>
-      </c>
-      <c r="O72" t="n">
-        <v>16</v>
-      </c>
-      <c r="P72" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4429,16 +4429,16 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>62</v>
+      </c>
+      <c r="D73" t="n">
+        <v>33</v>
+      </c>
+      <c r="E73" t="n">
         <v>2</v>
-      </c>
-      <c r="C73" t="n">
-        <v>52</v>
-      </c>
-      <c r="D73" t="n">
-        <v>28</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>5</v>
@@ -4459,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -4468,10 +4468,10 @@
         <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4479,26 +4479,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -4510,46 +4510,48 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
         <v>12</v>
       </c>
-      <c r="O74" t="n">
-        <v>16</v>
-      </c>
       <c r="P74" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -4558,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
+        <v>14</v>
+      </c>
+      <c r="O75" t="n">
         <v>16</v>
       </c>
-      <c r="O75" t="n">
-        <v>12</v>
-      </c>
       <c r="P75" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
@@ -4589,17 +4591,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -4608,13 +4610,13 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4623,55 +4625,53 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O76" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="n">
-        <v>2</v>
-      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
+        <v>39</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
         <v>2</v>
       </c>
-      <c r="D77" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
@@ -4679,43 +4679,45 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="M77" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O77" t="n">
         <v>16</v>
       </c>
       <c r="P77" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -4730,22 +4732,22 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M78" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O78" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -4753,26 +4755,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -4787,10 +4789,10 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>50</v>
+        <v>-2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N79" t="n">
         <v>8</v>
@@ -4799,40 +4801,42 @@
         <v>16</v>
       </c>
       <c r="P79" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4841,19 +4845,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M80" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>16</v>
       </c>
       <c r="P80" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -4861,32 +4865,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4895,45 +4899,43 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
         <v>16</v>
       </c>
-      <c r="O81" t="n">
-        <v>12</v>
-      </c>
       <c r="P81" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D82" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4951,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -4960,10 +4962,10 @@
         <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P82" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4971,20 +4973,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -4996,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -5005,19 +5007,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M83" t="n">
         <v>25</v>
       </c>
       <c r="N83" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P83" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -5025,77 +5027,79 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D84" t="n">
+        <v>22</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
         <v>30</v>
       </c>
-      <c r="E84" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>53</v>
-      </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P84" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Aneurin Donald</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D85" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5104,7 +5108,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -5113,19 +5117,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5133,17 +5137,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -5152,13 +5156,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5167,19 +5171,19 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O86" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P86" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -5187,26 +5191,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -5218,22 +5222,22 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -5241,20 +5245,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -5266,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -5275,19 +5279,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -5295,23 +5299,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -5320,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5329,19 +5333,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -5349,17 +5353,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -5368,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -5380,22 +5384,22 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N90" t="n">
+        <v>14</v>
+      </c>
+      <c r="O90" t="n">
         <v>8</v>
       </c>
-      <c r="O90" t="n">
-        <v>12</v>
-      </c>
       <c r="P90" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5403,20 +5407,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -5437,10 +5441,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M91" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -5449,7 +5453,7 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5457,17 +5461,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -5476,13 +5480,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5491,16 +5495,16 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N92" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P92" t="n">
         <v>29</v>
@@ -5511,33 +5515,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>2</v>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
@@ -5545,19 +5549,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P93" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5565,23 +5569,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D94" t="n">
         <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -5599,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -5611,7 +5615,7 @@
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -5619,23 +5623,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -5644,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5653,19 +5657,19 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -5673,7 +5677,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -5698,28 +5702,28 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O96" t="n">
         <v>8</v>
       </c>
       <c r="P96" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5727,17 +5731,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Moeen Ali</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -5752,28 +5756,28 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N97" t="n">
+        <v>6</v>
+      </c>
+      <c r="O97" t="n">
         <v>8</v>
       </c>
-      <c r="O97" t="n">
-        <v>4</v>
-      </c>
       <c r="P97" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -5781,17 +5785,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Moeen Ali</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -5806,28 +5810,28 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -5835,17 +5839,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -5860,28 +5864,28 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
+        <v>12</v>
+      </c>
+      <c r="O99" t="n">
         <v>8</v>
       </c>
-      <c r="O99" t="n">
-        <v>4</v>
-      </c>
       <c r="P99" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -5889,17 +5893,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -5914,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -5923,19 +5927,19 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -5943,17 +5947,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tom Kohler-Cadmore</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -5968,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5977,19 +5981,19 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
         <v>8</v>
       </c>
-      <c r="O101" t="n">
-        <v>4</v>
-      </c>
       <c r="P101" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -5997,17 +6001,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Tom Kohler-Cadmore</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -6031,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -6043,7 +6047,7 @@
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
@@ -6105,7 +6109,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -6130,7 +6134,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -6145,13 +6149,13 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
@@ -6159,56 +6163,164 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>4</v>
+      </c>
+      <c r="P105" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Liam Patterson-White</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>4</v>
+      </c>
+      <c r="P106" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
         <v>-2</v>
       </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>4</v>
-      </c>
-      <c r="P105" t="n">
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>4</v>
+      </c>
+      <c r="P107" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="n">
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6256,39 +6368,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="D3" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -6298,51 +6410,51 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
@@ -6351,112 +6463,112 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -6465,188 +6577,188 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
         <v>7</v>
-      </c>
-      <c r="E13" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -6655,131 +6767,131 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="D24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D28" t="n">
         <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -6788,39 +6900,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6882,10 +6994,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -6894,7 +7006,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -6914,7 +7026,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -6926,14 +7038,14 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -6942,14 +7054,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -6958,14 +7070,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -6974,14 +7086,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -6990,14 +7102,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -7006,14 +7118,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -7022,14 +7134,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -7038,14 +7150,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -7054,14 +7166,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -7070,14 +7182,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -7086,14 +7198,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -7102,14 +7214,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -7118,14 +7230,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -7134,14 +7246,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -7150,11 +7262,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
         <v>4</v>
@@ -7166,11 +7278,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
@@ -7182,7 +7294,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -7198,14 +7310,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -7214,14 +7326,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -7230,14 +7342,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -7246,14 +7358,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -7262,7 +7374,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -7278,7 +7390,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -7294,11 +7406,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
@@ -7310,7 +7422,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -7326,11 +7438,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -7350,7 +7462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7830,6 +7942,62 @@
         </is>
       </c>
       <c r="F17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Trent Rockets vs Sunrisers Leeds, 17th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Trent Rockets won by 5 runs</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MI London vs Manchester Super Giants, 18th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>MI London won by 45 runs</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7844,7 +8012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E352"/>
+  <dimension ref="A1:E395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15947,6 +16115,995 @@
         <v>12</v>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>17</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>17</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Nathan Ellis</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>17</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Finn Allen</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>17</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Brydon Carse</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>17</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Aneurin Donald</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>17</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Sam Billings</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>17</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>17</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>17</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>17</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>17</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Liam Patterson-White</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>17</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>17</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Mitchell Marsh</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>17</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Ryan Rickelton</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>17</v>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Mohammad Amir</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>17</v>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>17</v>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>17</v>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Tom Alsop</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>17</v>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Craig Overton</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>17</v>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>17</v>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Calvin Harrison</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>17</v>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Lewis Gregory</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>18</v>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>18</v>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>18</v>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>18</v>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Sonny Baker</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>18</v>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Nicholas Pooran</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>18</v>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Josh Tongue</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>18</v>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Sam Curran</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>18</v>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Jos Buttler</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>18</v>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Sherfane Rutherford</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>18</v>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Leus du Plooy</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>18</v>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Tom Curran</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>18</v>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Rashid Khan</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>18</v>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Gus Atkinson</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>18</v>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Liam Dawson</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>18</v>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>18</v>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>18</v>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Nathan Sowter</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>18</v>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Heinrich Klaasen</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>18</v>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>18</v>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Trent Boult</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>18</v>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Richard Gleeson</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -519,19 +519,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>9</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="M2" t="n">
         <v>260</v>
@@ -558,67 +558,69 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>372</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>456</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="D3" t="n">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>331</v>
+        <v>182</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O3" t="n">
         <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -627,23 +629,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D4" t="n">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -652,54 +654,56 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -708,28 +712,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
@@ -739,23 +743,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -764,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -773,78 +777,78 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>184</v>
+        <v>301</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -963,81 +967,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="N10" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P10" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>7</v>
@@ -1052,168 +1052,172 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M11" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="n">
+        <v>132</v>
+      </c>
+      <c r="D12" t="n">
+        <v>67</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="M12" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="O12" t="n">
         <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
@@ -1221,55 +1225,53 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>123</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
@@ -1277,273 +1279,277 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="M16" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O16" t="n">
         <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>253</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>77</v>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M17" t="n">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N18" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>237</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
         <v>6</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N19" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>229</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>145</v>
+      </c>
+      <c r="D20" t="n">
+        <v>119</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>5</v>
       </c>
-      <c r="C20" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
@@ -1551,19 +1557,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="M20" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P20" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -1571,128 +1577,132 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>124</v>
+      </c>
+      <c r="D21" t="n">
+        <v>77</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>5</v>
       </c>
-      <c r="C21" t="n">
-        <v>39</v>
-      </c>
-      <c r="D21" t="n">
-        <v>30</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="M21" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P21" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="M22" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>211</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1704,28 +1714,28 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O23" t="n">
         <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -1733,32 +1743,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1767,19 +1777,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O24" t="n">
         <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -1787,53 +1797,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M25" t="n">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -1841,90 +1851,86 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>6</v>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1933,108 +1939,110 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="M28" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
         <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2043,45 +2051,43 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M29" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D30" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2099,7 +2105,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2108,10 +2114,10 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2121,88 +2127,86 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O31" t="n">
         <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>182</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2211,19 +2215,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2231,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -2256,7 +2260,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2265,47 +2269,49 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O33" t="n">
         <v>20</v>
       </c>
       <c r="P33" t="n">
-        <v>179</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>6</v>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -2319,19 +2325,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="N34" t="n">
         <v>8</v>
       </c>
       <c r="O34" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P34" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -2339,77 +2345,79 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="M35" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
-        <v>174</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D36" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F36" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -2418,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2427,54 +2435,52 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P36" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2483,52 +2489,54 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="M37" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>20</v>
       </c>
       <c r="P37" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="D38" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2537,110 +2545,106 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P38" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>-2</v>
+        <v>53</v>
       </c>
       <c r="M39" t="n">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O39" t="n">
         <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2649,52 +2653,54 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="M40" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2703,19 +2709,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M41" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -2723,17 +2729,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2757,73 +2763,75 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M42" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="N42" t="n">
         <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P42" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
         <v>15</v>
       </c>
-      <c r="D43" t="n">
-        <v>11</v>
-      </c>
       <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>2</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M43" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="N43" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P43" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -2831,32 +2839,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2865,56 +2873,52 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N44" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P44" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
         <v>5</v>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2923,50 +2927,46 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O45" t="n">
         <v>20</v>
       </c>
       <c r="P45" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="D46" t="n">
+        <v>57</v>
+      </c>
+      <c r="E46" t="n">
         <v>9</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2978,46 +2978,50 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="M46" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="O46" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P46" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D47" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -3026,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3035,43 +3039,47 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P47" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
@@ -3080,54 +3088,52 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N48" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="O48" t="n">
         <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="E49" t="n">
         <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3136,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3145,19 +3151,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P49" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -3165,63 +3171,61 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E50" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P50" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3231,10 +3235,10 @@
         <v>99</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
         <v>7</v>
@@ -3255,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3267,7 +3271,7 @@
         <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3275,26 +3279,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
         <v>3</v>
-      </c>
-      <c r="F52" t="n">
-        <v>6</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -3306,55 +3310,57 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N52" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O52" t="n">
         <v>16</v>
       </c>
       <c r="P52" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D53" t="n">
+        <v>53</v>
+      </c>
+      <c r="E53" t="n">
         <v>6</v>
       </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3363,19 +3369,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="M53" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O53" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P53" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -3383,23 +3389,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D54" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3417,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3429,31 +3435,33 @@
         <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D55" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -3462,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3471,19 +3479,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>16</v>
       </c>
       <c r="P55" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3491,23 +3499,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D56" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -3516,53 +3524,49 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" t="n">
         <v>6</v>
       </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3580,22 +3584,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M57" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N57" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P57" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3607,13 +3611,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D58" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E58" t="n">
         <v>4</v>
@@ -3637,7 +3641,7 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -3646,10 +3650,10 @@
         <v>24</v>
       </c>
       <c r="O58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P58" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -3657,32 +3661,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
       <c r="G59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3691,19 +3695,19 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="M59" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O59" t="n">
         <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3711,23 +3715,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3736,49 +3740,53 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P60" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
         <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3790,84 +3798,82 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M61" t="n">
         <v>103</v>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P61" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>69</v>
+      </c>
+      <c r="D62" t="n">
+        <v>46</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" t="n">
         <v>3</v>
       </c>
-      <c r="C62" t="n">
-        <v>64</v>
-      </c>
-      <c r="D62" t="n">
-        <v>50</v>
-      </c>
-      <c r="E62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2</v>
-      </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M62" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O62" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P62" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3875,26 +3881,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3906,27 +3912,27 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3935,13 +3941,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3965,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M64" t="n">
         <v>83</v>
@@ -3974,10 +3980,10 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P64" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
@@ -3987,26 +3993,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -4021,37 +4027,39 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M65" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P65" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -4075,10 +4083,10 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N66" t="n">
         <v>8</v>
@@ -4087,7 +4095,7 @@
         <v>20</v>
       </c>
       <c r="P66" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4095,17 +4103,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -4129,19 +4137,19 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N67" t="n">
         <v>8</v>
       </c>
       <c r="O67" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P67" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -4149,32 +4157,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D68" t="n">
+        <v>46</v>
+      </c>
+      <c r="E68" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" t="n">
         <v>3</v>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4183,46 +4191,48 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="M68" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O68" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P68" t="n">
         <v>111</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -4237,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -4249,24 +4259,22 @@
         <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -4284,7 +4292,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -4293,39 +4301,37 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O70" t="n">
         <v>16</v>
       </c>
       <c r="P70" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -4340,28 +4346,28 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M71" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O71" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P71" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -4369,24 +4375,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>75</v>
+      </c>
+      <c r="D72" t="n">
+        <v>57</v>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
         <v>5</v>
       </c>
-      <c r="C72" t="n">
-        <v>66</v>
-      </c>
-      <c r="D72" t="n">
-        <v>44</v>
-      </c>
-      <c r="E72" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" t="n">
-        <v>3</v>
-      </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
@@ -4403,7 +4409,7 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4412,45 +4418,45 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P72" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
         <v>3</v>
       </c>
-      <c r="C73" t="n">
-        <v>62</v>
-      </c>
-      <c r="D73" t="n">
-        <v>33</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4459,52 +4465,54 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>79</v>
+        <v>-2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P73" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4513,75 +4521,73 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="M74" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O74" t="n">
         <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="D75" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
@@ -4591,86 +4597,88 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P76" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4679,78 +4687,78 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N77" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="O77" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P77" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>2</v>
-      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>2</v>
       </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="M78" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
         <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5353,53 +5361,53 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>2</v>
       </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5407,20 +5415,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -5432,28 +5440,28 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O91" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5461,20 +5469,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -5495,10 +5503,10 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M92" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -5507,7 +5515,7 @@
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5515,21 +5523,21 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Tom Kohler-Cadmore</t>
         </is>
       </c>
       <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="n">
+        <v>24</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" t="n">
         <v>3</v>
       </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="n">
-        <v>5</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
@@ -5540,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5549,19 +5557,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P93" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -5569,33 +5577,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>2</v>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
@@ -5603,19 +5611,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P94" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -5623,26 +5631,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -5657,10 +5665,10 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -5669,7 +5677,7 @@
         <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -5677,21 +5685,21 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>22</v>
+      </c>
+      <c r="D96" t="n">
+        <v>19</v>
+      </c>
+      <c r="E96" t="n">
         <v>2</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
@@ -5702,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -5711,19 +5719,19 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5731,23 +5739,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -5762,22 +5770,22 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -5785,17 +5793,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Moeen Ali</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -5810,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -5819,19 +5827,19 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
+        <v>16</v>
+      </c>
+      <c r="O98" t="n">
         <v>8</v>
       </c>
-      <c r="O98" t="n">
-        <v>4</v>
-      </c>
       <c r="P98" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -5839,17 +5847,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Moeen Ali</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -5864,82 +5872,84 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
         <v>8</v>
       </c>
       <c r="P99" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>8</v>
+      </c>
+      <c r="N100" t="n">
         <v>6</v>
       </c>
-      <c r="D100" t="n">
-        <v>4</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>6</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
+      <c r="O100" t="n">
         <v>8</v>
       </c>
-      <c r="O100" t="n">
-        <v>4</v>
-      </c>
       <c r="P100" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -5947,17 +5957,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -5972,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -5981,19 +5991,19 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O101" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -6001,17 +6011,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tom Kohler-Cadmore</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -6026,7 +6036,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -6035,19 +6045,19 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
         <v>8</v>
       </c>
-      <c r="O102" t="n">
-        <v>4</v>
-      </c>
       <c r="P102" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
@@ -6467,7 +6477,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>145</v>
@@ -6482,17 +6492,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
@@ -6501,39 +6511,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -6558,17 +6568,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
@@ -6577,172 +6587,172 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D17" t="n">
+        <v>12</v>
+      </c>
+      <c r="E17" t="n">
         <v>7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -6752,13 +6762,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
         <v>4</v>
@@ -6767,45 +6777,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -6815,7 +6825,7 @@
         <v>99</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>7</v>
@@ -6824,115 +6834,115 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="D28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6978,7 +6988,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
@@ -7006,14 +7016,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -7022,11 +7032,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
@@ -7038,7 +7048,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -7054,14 +7064,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -7070,7 +7080,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7102,11 +7112,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
@@ -7118,7 +7128,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -7134,14 +7144,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -7150,14 +7160,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -7166,7 +7176,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -7182,7 +7192,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7198,11 +7208,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
@@ -7214,11 +7224,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
@@ -7230,7 +7240,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7246,11 +7256,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>5</v>
@@ -7262,14 +7272,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -7278,14 +7288,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
         <v>5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>4</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -7310,11 +7320,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
         <v>4</v>
@@ -7326,11 +7336,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
         <v>4</v>
@@ -7342,7 +7352,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -7358,11 +7368,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
         <v>4</v>
@@ -7374,14 +7384,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -7390,14 +7400,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -7406,14 +7416,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -7438,11 +7448,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
         <v>3</v>
@@ -7462,7 +7472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7998,6 +8008,34 @@
         </is>
       </c>
       <c r="F19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Welsh Fire vs Southern Brave, 19th Match, The Hundred Mens Competition 2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Welsh Fire won by 6 wkts</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8012,7 +8050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E395"/>
+  <dimension ref="A1:E417"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17104,6 +17142,512 @@
         <v>29</v>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>19</v>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>19</v>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>19</v>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>19</v>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Nikhil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>19</v>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>19</v>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>19</v>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>19</v>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Rachin Ravindra</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>19</v>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Moeen Ali</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>19</v>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>19</v>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>19</v>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>19</v>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>19</v>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>19</v>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>19</v>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Chris Woakes</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="n">
+        <v>19</v>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Sam Cook</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="n">
+        <v>19</v>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Matthew Short</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="n">
+        <v>19</v>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Philip Salt</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="n">
+        <v>19</v>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="n">
+        <v>19</v>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Tom Kohler-Cadmore</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="n">
+        <v>19</v>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/hundred_player_stats.xlsx
+++ b/hundred_player_stats.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R107"/>
+  <dimension ref="A1:R108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,114 +571,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>182</v>
+        <v>412</v>
       </c>
       <c r="M3" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>376</v>
+        <v>440</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="D4" t="n">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>331</v>
+        <v>182</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -687,23 +685,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D5" t="n">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -712,54 +710,56 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D6" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -768,28 +768,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
         <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -799,23 +799,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -833,112 +833,110 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="M8" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="N8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -947,46 +945,50 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>274</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+        <v>304</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -998,324 +1000,326 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>271</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>276</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>9</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="N12" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P12" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="M13" t="n">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>266</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <v>269</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="M14" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="O14" t="n">
         <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>259</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="D15" t="n">
+        <v>91</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="M15" t="n">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1324,28 +1328,28 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
         <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1357,33 +1361,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -1391,55 +1395,53 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>123</v>
-      </c>
-      <c r="D18" t="n">
-        <v>90</v>
-      </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
@@ -1447,156 +1449,160 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="M19" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O19" t="n">
         <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>253</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="D20" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>96</v>
+      </c>
+      <c r="M20" t="n">
+        <v>136</v>
+      </c>
+      <c r="N20" t="n">
         <v>8</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>175</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>40</v>
-      </c>
       <c r="O20" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
         <v>6</v>
-      </c>
-      <c r="C21" t="n">
-        <v>124</v>
-      </c>
-      <c r="D21" t="n">
-        <v>77</v>
-      </c>
-      <c r="E21" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1608,48 +1614,46 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>163</v>
+        <v>28</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N21" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D22" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1658,28 +1662,28 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -1689,87 +1693,89 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>124</v>
+      </c>
+      <c r="D23" t="n">
+        <v>77</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>5</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M23" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P23" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>145</v>
+      </c>
+      <c r="D24" t="n">
+        <v>119</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>15</v>
-      </c>
-      <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
@@ -1777,19 +1783,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="M24" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P24" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -1797,32 +1803,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1831,94 +1837,98 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>43</v>
+        <v>-2</v>
       </c>
       <c r="M25" t="n">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="M26" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>211</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1930,28 +1940,28 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O27" t="n">
         <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -1959,33 +1969,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
@@ -1993,77 +2003,73 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O28" t="n">
         <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>6</v>
-      </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>141</v>
+      </c>
+      <c r="N29" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" t="n">
         <v>20</v>
       </c>
-      <c r="M29" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" t="n">
-        <v>60</v>
-      </c>
-      <c r="O29" t="n">
-        <v>24</v>
-      </c>
       <c r="P29" t="n">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -2071,23 +2077,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2096,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2105,42 +2111,40 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" t="n">
         <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -2158,22 +2162,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M31" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
         <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -2181,32 +2185,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2215,19 +2219,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2235,26 +2239,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="D33" t="n">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -2269,10 +2273,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N33" t="n">
         <v>24</v>
@@ -2281,36 +2285,34 @@
         <v>20</v>
       </c>
       <c r="P33" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -2325,10 +2327,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M34" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>8</v>
@@ -2337,88 +2339,90 @@
         <v>20</v>
       </c>
       <c r="P34" t="n">
-        <v>194</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="D35" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>6</v>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="O35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P35" t="n">
-        <v>192</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D36" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E36" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" t="n">
         <v>8</v>
       </c>
-      <c r="F36" t="n">
-        <v>4</v>
-      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
@@ -2426,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2435,108 +2439,108 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P36" t="n">
-        <v>190</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O37" t="n">
         <v>20</v>
       </c>
       <c r="P37" t="n">
-        <v>182</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2545,19 +2549,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="M38" t="n">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
         <v>20</v>
       </c>
       <c r="P38" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -2565,86 +2569,88 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="E39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2</v>
-      </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="M39" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P39" t="n">
-        <v>174</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2653,54 +2659,52 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P40" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="n">
+        <v>125</v>
+      </c>
+      <c r="D41" t="n">
+        <v>84</v>
+      </c>
+      <c r="E41" t="n">
         <v>12</v>
       </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2709,52 +2713,54 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="M41" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O41" t="n">
         <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>108</v>
+      </c>
+      <c r="D42" t="n">
+        <v>92</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2763,102 +2769,102 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>-2</v>
+        <v>134</v>
       </c>
       <c r="M42" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P42" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
+        <v>117</v>
+      </c>
+      <c r="D43" t="n">
+        <v>92</v>
+      </c>
+      <c r="E43" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>154</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>8</v>
+      </c>
+      <c r="O43" t="n">
         <v>20</v>
       </c>
-      <c r="D43" t="n">
-        <v>15</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>23</v>
-      </c>
-      <c r="M43" t="n">
-        <v>108</v>
-      </c>
-      <c r="N43" t="n">
-        <v>16</v>
-      </c>
-      <c r="O43" t="n">
-        <v>16</v>
-      </c>
       <c r="P43" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2873,40 +2879,42 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="M44" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P44" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2918,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2927,19 +2935,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M45" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="N45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>20</v>
       </c>
       <c r="P45" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -2947,90 +2955,86 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" t="n">
+        <v>34</v>
+      </c>
+      <c r="E46" t="n">
         <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>79</v>
-      </c>
-      <c r="D46" t="n">
-        <v>57</v>
-      </c>
-      <c r="E46" t="n">
-        <v>9</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N46" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>5</v>
       </c>
       <c r="C47" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3039,42 +3043,38 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
         <v>20</v>
       </c>
       <c r="P47" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="n">
         <v>4</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>5</v>
       </c>
-      <c r="D48" t="n">
-        <v>9</v>
-      </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
@@ -3082,34 +3082,34 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>5</v>
-      </c>
       <c r="M48" t="n">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="N48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P48" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -3117,23 +3117,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D49" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3151,52 +3151,56 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+        <v>157</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>4</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -3205,46 +3209,48 @@
         <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="N50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O50" t="n">
         <v>20</v>
       </c>
       <c r="P50" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -3259,19 +3265,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N51" t="n">
         <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P51" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -3279,32 +3285,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -3313,21 +3319,23 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="M52" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P52" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
@@ -3335,24 +3343,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>95</v>
+      </c>
+      <c r="D53" t="n">
+        <v>62</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>87</v>
-      </c>
-      <c r="D53" t="n">
-        <v>53</v>
-      </c>
-      <c r="E53" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" t="n">
-        <v>7</v>
-      </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
@@ -3360,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -3369,43 +3377,47 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P53" t="n">
-        <v>152</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+        <v>154</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D54" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3423,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -3432,66 +3444,64 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P54" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>4</v>
       </c>
-      <c r="C55" t="n">
-        <v>99</v>
-      </c>
-      <c r="D55" t="n">
-        <v>63</v>
-      </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
         <v>7</v>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>127</v>
-      </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P55" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -3499,26 +3509,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
         <v>3</v>
-      </c>
-      <c r="F56" t="n">
-        <v>6</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -3530,55 +3540,57 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N56" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D57" t="n">
+        <v>53</v>
+      </c>
+      <c r="E57" t="n">
         <v>6</v>
       </c>
-      <c r="E57" t="n">
-        <v>2</v>
-      </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3587,19 +3599,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="M57" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P57" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -3607,24 +3619,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D58" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="n">
         <v>4</v>
       </c>
-      <c r="F58" t="n">
-        <v>5</v>
-      </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
@@ -3632,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3641,44 +3653,46 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
       <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D59" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="n">
         <v>6</v>
       </c>
-      <c r="F59" t="n">
-        <v>2</v>
-      </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
@@ -3686,28 +3700,28 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="O59" t="n">
         <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -3715,27 +3729,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>4</v>
       </c>
-      <c r="C60" t="n">
-        <v>95</v>
-      </c>
-      <c r="D60" t="n">
-        <v>62</v>
-      </c>
-      <c r="E60" t="n">
-        <v>10</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
@@ -3749,56 +3763,52 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="n">
+        <v>82</v>
+      </c>
+      <c r="D61" t="n">
+        <v>51</v>
+      </c>
+      <c r="E61" t="n">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
-        <v>12</v>
-      </c>
-      <c r="D61" t="n">
-        <v>9</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3807,19 +3817,19 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="M61" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P61" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -3827,23 +3837,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D62" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -3852,28 +3862,28 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P62" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -3881,17 +3891,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3912,101 +3922,99 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="N63" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P63" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>107</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
         <v>8</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>13</v>
-      </c>
-      <c r="M64" t="n">
-        <v>83</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
       <c r="O64" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P64" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D65" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -4018,48 +4026,46 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O65" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P65" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -4068,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -4080,46 +4086,48 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
         <v>3</v>
@@ -4128,7 +4136,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -4137,52 +4145,54 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M67" t="n">
         <v>83</v>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P67" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4191,45 +4201,43 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P68" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>3</v>
-      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -4238,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -4247,19 +4255,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>86</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P69" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4267,17 +4275,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -4301,19 +4309,19 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N70" t="n">
         <v>8</v>
       </c>
       <c r="O70" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P70" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -4321,17 +4329,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>5</v>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -4352,111 +4360,111 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="M71" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="N71" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>20</v>
       </c>
       <c r="P71" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B72" t="n">
+        <v>5</v>
+      </c>
+      <c r="C72" t="n">
         <v>4</v>
       </c>
-      <c r="C72" t="n">
+      <c r="D72" t="n">
+        <v>4</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>4</v>
+      </c>
+      <c r="M72" t="n">
         <v>75</v>
       </c>
-      <c r="D72" t="n">
-        <v>57</v>
-      </c>
-      <c r="E72" t="n">
-        <v>6</v>
-      </c>
-      <c r="F72" t="n">
-        <v>5</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>94</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O72" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P72" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -4465,54 +4473,54 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>-2</v>
+        <v>79</v>
       </c>
       <c r="M73" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P73" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="n">
         <v>3</v>
       </c>
-      <c r="C74" t="n">
-        <v>62</v>
-      </c>
-      <c r="D74" t="n">
-        <v>33</v>
-      </c>
-      <c r="E74" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" t="n">
-        <v>5</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -4521,52 +4529,54 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N74" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P74" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D75" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -4575,24 +4585,22 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="M75" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
         <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4601,13 +4609,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C76" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D76" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E76" t="n">
         <v>9</v>
@@ -4631,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -4640,10 +4648,10 @@
         <v>14</v>
       </c>
       <c r="O76" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P76" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
@@ -4653,32 +4661,32 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -4687,19 +4695,19 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M77" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N77" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P77" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -4707,32 +4715,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4741,39 +4749,37 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O78" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>2</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -4782,13 +4788,13 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4797,45 +4803,43 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O79" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P79" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="n">
-        <v>2</v>
-      </c>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D80" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E80" t="n">
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -4844,7 +4848,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -4853,37 +4857,39 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O80" t="n">
         <v>16</v>
       </c>
       <c r="P80" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>4</v>
       </c>
       <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
         <v>4</v>
-      </c>
-      <c r="D81" t="n">
-        <v>9</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -4898,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4907,43 +4913,45 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="M81" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O81" t="n">
         <v>16</v>
       </c>
       <c r="P81" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D82" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -4961,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -4973,7 +4981,7 @@
         <v>16</v>
       </c>
       <c r="P82" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -4981,32 +4989,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>4</v>
       </c>
       <c r="C83" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" t="n">
         <v>9</v>
       </c>
-      <c r="D83" t="n">
-        <v>6</v>
-      </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -5015,19 +5023,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M83" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N83" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>16</v>
       </c>
       <c r="P83" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -5035,26 +5043,26 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Reece Topley</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -5069,45 +5077,43 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N84" t="n">
         <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P84" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aneurin Donald</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C85" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D85" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -5116,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -5125,19 +5131,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="P85" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -5145,53 +5151,53 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Aneurin Donald</t>
         </is>
       </c>
       <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>40</v>
+      </c>
+      <c r="D86" t="n">
+        <v>19</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>54</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
         <v>4</v>
       </c>
-      <c r="C86" t="n">
-        <v>24</v>
-      </c>
-      <c r="D86" t="n">
-        <v>26</v>
-      </c>
-      <c r="E86" t="n">
-        <v>1</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>25</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="n">
-        <v>16</v>
-      </c>
-      <c r="O86" t="n">
-        <v>16</v>
-      </c>
       <c r="P86" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -5199,23 +5205,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D87" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -5224,7 +5230,7 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -5233,53 +5239,55 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O87" t="n">
         <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B88" t="n">
+        <v>4</v>
+      </c>
+      <c r="C88" t="n">
+        <v>24</v>
+      </c>
+      <c r="D88" t="n">
+        <v>26</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
         <v>2</v>
       </c>
-      <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>1</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" t="n">
-        <v>3</v>
-      </c>
       <c r="J88" t="n">
         <v>0</v>
       </c>
@@ -5287,16 +5295,16 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M88" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O88" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P88" t="n">
         <v>57</v>
@@ -5307,23 +5315,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D89" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E89" t="n">
         <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -5332,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5341,16 +5349,16 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P89" t="n">
         <v>57</v>
@@ -5361,23 +5369,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -5386,28 +5394,28 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -5415,53 +5423,53 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B91" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
         <v>2</v>
       </c>
-      <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
-        <v>1</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
       <c r="L91" t="n">
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P91" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -5469,20 +5477,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -5494,28 +5502,28 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P92" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -5577,32 +5585,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5611,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N94" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -5631,17 +5639,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -5650,13 +5658,13 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5665,16 +5673,16 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P95" t="n">
         <v>29</v>
@@ -5685,26 +5693,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -5719,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -5731,7 +5739,7 @@
         <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -5739,23 +5747,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D97" t="n">
         <v>19</v>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -5773,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -5785,7 +5793,7 @@
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -5793,23 +5801,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -5818,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -5827,19 +5835,19 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -5847,17 +5855,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Moeen Ali</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -5872,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -5881,39 +5889,37 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O99" t="n">
         <v>8</v>
       </c>